--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dave\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33CB507-C79D-4410-89FE-4C83A103F217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E386E2E6-EEEF-45E1-980B-09208BFE00BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="169">
   <si>
     <t>London</t>
   </si>
@@ -524,6 +524,24 @@
   </si>
   <si>
     <t>Newbury</t>
+  </si>
+  <si>
+    <t>The Barrel Vault</t>
+  </si>
+  <si>
+    <t>St Pancras</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>fr</t>
+  </si>
+  <si>
+    <t>Le Viaduc</t>
+  </si>
+  <si>
+    <t>Le Paris Lyon</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1073,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1079,7 +1097,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1103,7 +1121,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1163,7 +1181,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2859,11 +2877,24 @@
       <c r="A110" s="8">
         <v>109</v>
       </c>
+      <c r="B110" s="1">
+        <v>46144</v>
+      </c>
+      <c r="C110" t="s">
+        <v>163</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>110</v>
       </c>
+      <c r="D111" s="2"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
@@ -3945,10 +3976,34 @@
       <c r="A20" s="8">
         <v>19</v>
       </c>
+      <c r="B20" s="1">
+        <v>46144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46144</v>
+      </c>
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E386E2E6-EEEF-45E1-980B-09208BFE00BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E18F8CA-4D26-470C-A791-BF9AB8700798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="173">
   <si>
     <t>London</t>
   </si>
@@ -542,6 +542,18 @@
   </si>
   <si>
     <t>Le Paris Lyon</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Novotel</t>
+  </si>
+  <si>
+    <t>Delirium Café</t>
+  </si>
+  <si>
+    <t>The Thirsty Monk</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1109,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1121,7 +1133,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4010,15 +4022,51 @@
       <c r="A22" s="8">
         <v>21</v>
       </c>
+      <c r="B22" s="1">
+        <v>46145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>22</v>
       </c>
+      <c r="B23" s="1">
+        <v>46145</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46145</v>
+      </c>
+      <c r="C24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E18F8CA-4D26-470C-A791-BF9AB8700798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC55C117-3C2F-40B3-8616-EE3B699C27CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="178">
   <si>
     <t>London</t>
   </si>
@@ -554,6 +554,21 @@
   </si>
   <si>
     <t>The Thirsty Monk</t>
+  </si>
+  <si>
+    <t>Le Bar à Vin</t>
+  </si>
+  <si>
+    <t>The Frog &amp; Rosbif</t>
+  </si>
+  <si>
+    <t>La Taverne du Midi</t>
+  </si>
+  <si>
+    <t>La Route du Rhum</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1124,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1133,7 +1148,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4073,26 +4088,86 @@
       <c r="A25" s="8">
         <v>24</v>
       </c>
+      <c r="B25" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>25</v>
       </c>
+      <c r="B26" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>26</v>
       </c>
+      <c r="B27" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>27</v>
       </c>
+      <c r="B28" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>28</v>
       </c>
+      <c r="B29" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C29" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
@@ -4928,12 +5003,12 @@
       <c r="A196" s="8">
         <v>195</v>
       </c>
-      <c r="E196"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>196</v>
       </c>
+      <c r="E197"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC55C117-3C2F-40B3-8616-EE3B699C27CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086BD74E-86A1-4B9D-9CCF-51096E405CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="180">
   <si>
     <t>London</t>
   </si>
@@ -569,6 +569,12 @@
   </si>
   <si>
     <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>Beer Trotter</t>
+  </si>
+  <si>
+    <t>Le Karadoc</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1130,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1148,7 +1154,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4173,10 +4179,34 @@
       <c r="A30" s="8">
         <v>29</v>
       </c>
+      <c r="B30" s="1">
+        <v>46147</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46147</v>
+      </c>
+      <c r="C31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086BD74E-86A1-4B9D-9CCF-51096E405CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131A64B9-1F36-4769-A1B5-8F5915B498A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="192">
   <si>
     <t>London</t>
   </si>
@@ -575,6 +575,42 @@
   </si>
   <si>
     <t>Le Karadoc</t>
+  </si>
+  <si>
+    <t>Bar El Brillante</t>
+  </si>
+  <si>
+    <t>Bar Cafetería Diego</t>
+  </si>
+  <si>
+    <t>Taberna Los Castizos</t>
+  </si>
+  <si>
+    <t>Vermutería Black Bolita</t>
+  </si>
+  <si>
+    <t>Taberna Salamanca</t>
+  </si>
+  <si>
+    <t>Taberna La Cava</t>
+  </si>
+  <si>
+    <t>La Chata</t>
+  </si>
+  <si>
+    <t>De Bodega</t>
+  </si>
+  <si>
+    <t>Taberna Del Tuerto</t>
+  </si>
+  <si>
+    <t>Mesón La Revolcona</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>es</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1166,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1154,7 +1190,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4213,83 +4249,203 @@
       <c r="A32" s="8">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B39" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B40" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B41" s="1">
+        <v>46179</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
+        <v>190</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>47</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131A64B9-1F36-4769-A1B5-8F5915B498A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8908E69-14C7-40DA-9D37-B2EAA1E09BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="199">
   <si>
     <t>London</t>
   </si>
@@ -611,6 +611,27 @@
   </si>
   <si>
     <t>es</t>
+  </si>
+  <si>
+    <t>Hostal La Colegiata</t>
+  </si>
+  <si>
+    <t>Socairo Taperia</t>
+  </si>
+  <si>
+    <t>A birreria</t>
+  </si>
+  <si>
+    <t>Garatuxa</t>
+  </si>
+  <si>
+    <t>Victoria </t>
+  </si>
+  <si>
+    <t>Bar El Castro</t>
+  </si>
+  <si>
+    <t>Vigo</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1187,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1190,7 +1211,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4419,30 +4440,102 @@
       <c r="A42" s="8">
         <v>41</v>
       </c>
+      <c r="B42" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C42" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>42</v>
       </c>
+      <c r="B43" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>43</v>
       </c>
+      <c r="B44" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C44" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>44</v>
       </c>
+      <c r="B45" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" t="s">
+        <v>198</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>45</v>
       </c>
+      <c r="B46" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C46" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" t="s">
+        <v>198</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C47" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8908E69-14C7-40DA-9D37-B2EAA1E09BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBEC382-BC62-4670-8CA1-DB4DC822E9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -625,13 +625,13 @@
     <t>Garatuxa</t>
   </si>
   <si>
-    <t>Victoria </t>
-  </si>
-  <si>
     <t>Bar El Castro</t>
   </si>
   <si>
     <t>Vigo</t>
+  </si>
+  <si>
+    <t>Restaurante A Pintxoteca</t>
   </si>
 </sst>
 </file>
@@ -4447,7 +4447,7 @@
         <v>192</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>191</v>
@@ -4464,7 +4464,7 @@
         <v>193</v>
       </c>
       <c r="D43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>191</v>
@@ -4481,7 +4481,7 @@
         <v>194</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>191</v>
@@ -4498,7 +4498,7 @@
         <v>195</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>191</v>
@@ -4512,10 +4512,10 @@
         <v>46181</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>191</v>
@@ -4529,10 +4529,10 @@
         <v>46181</v>
       </c>
       <c r="C47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s">
         <v>197</v>
-      </c>
-      <c r="D47" t="s">
-        <v>198</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>191</v>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBEC382-BC62-4670-8CA1-DB4DC822E9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A295578-F90C-4F99-B7B5-D907B1F55914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="203">
   <si>
     <t>London</t>
   </si>
@@ -632,6 +632,18 @@
   </si>
   <si>
     <t>Restaurante A Pintxoteca</t>
+  </si>
+  <si>
+    <t>Alta Fidelidad Ingravitto Café Bar</t>
+  </si>
+  <si>
+    <t>Salón de Café Grettel</t>
+  </si>
+  <si>
+    <t>Soportales Vinotales</t>
+  </si>
+  <si>
+    <t>Buenavista Bar</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1199,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1211,7 +1223,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4542,83 +4554,131 @@
       <c r="A48" s="8">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B48" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C48" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B49" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C49" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B50" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C50" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B51" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C51" t="s">
+        <v>202</v>
+      </c>
+      <c r="D51" t="s">
+        <v>197</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>63</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A295578-F90C-4F99-B7B5-D907B1F55914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C119AA54-94E2-412F-98C8-926589EB1991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
   <si>
     <t>London</t>
   </si>
@@ -644,6 +644,24 @@
   </si>
   <si>
     <t>Buenavista Bar</t>
+  </si>
+  <si>
+    <t>Theophilu's Bar</t>
+  </si>
+  <si>
+    <t>CAL Craft Beers</t>
+  </si>
+  <si>
+    <t>Cervejaria Nortada</t>
+  </si>
+  <si>
+    <t>Cândido dos Reis Cafe</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>pt</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1217,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1223,7 +1241,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4622,20 +4640,68 @@
       <c r="A52" s="8">
         <v>51</v>
       </c>
+      <c r="B52" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C52" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>52</v>
       </c>
+      <c r="B53" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D53" t="s">
+        <v>207</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>53</v>
       </c>
+      <c r="B54" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D55" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C119AA54-94E2-412F-98C8-926589EB1991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DF1AB4-34A1-4E5D-99EF-8DD0992E7573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="213">
   <si>
     <t>London</t>
   </si>
@@ -662,6 +662,18 @@
   </si>
   <si>
     <t>pt</t>
+  </si>
+  <si>
+    <t>Mercado do Bolhão</t>
+  </si>
+  <si>
+    <t>Vinhos Quinta do Nova</t>
+  </si>
+  <si>
+    <t>Caves Cálem</t>
+  </si>
+  <si>
+    <t>Casta D’ouro</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1229,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1241,7 +1253,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4708,20 +4720,68 @@
       <c r="A56" s="8">
         <v>55</v>
       </c>
+      <c r="B56" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C56" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>56</v>
       </c>
+      <c r="B57" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C57" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>57</v>
       </c>
+      <c r="B58" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C58" t="s">
+        <v>211</v>
+      </c>
+      <c r="D58" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C59" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DF1AB4-34A1-4E5D-99EF-8DD0992E7573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066D94F-DFF4-41AE-BDB6-75F88B08E48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="217">
   <si>
     <t>London</t>
   </si>
@@ -674,6 +674,18 @@
   </si>
   <si>
     <t>Casta D’ouro</t>
+  </si>
+  <si>
+    <t>Hotel Douro</t>
+  </si>
+  <si>
+    <t>Quinta das Carvalhas</t>
+  </si>
+  <si>
+    <t>Armazém da Cerveja</t>
+  </si>
+  <si>
+    <t>Pinhão</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1241,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1253,7 +1265,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4788,15 +4800,51 @@
       <c r="A60" s="8">
         <v>59</v>
       </c>
+      <c r="B60" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C60" t="s">
+        <v>213</v>
+      </c>
+      <c r="D60" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>60</v>
       </c>
+      <c r="B61" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C61" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066D94F-DFF4-41AE-BDB6-75F88B08E48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D417EB4-E136-4DC2-BB7D-D63CC609D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="221">
   <si>
     <t>London</t>
   </si>
@@ -686,6 +686,18 @@
   </si>
   <si>
     <t>Pinhão</t>
+  </si>
+  <si>
+    <t>The Calleva Arms</t>
+  </si>
+  <si>
+    <t>Silchester</t>
+  </si>
+  <si>
+    <t>The George &amp; Dragon</t>
+  </si>
+  <si>
+    <t>Wolverton Townsend</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1229,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1265,7 +1277,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3038,11 +3050,28 @@
       <c r="A111" s="8">
         <v>110</v>
       </c>
-      <c r="D111" s="2"/>
+      <c r="B111" s="1">
+        <v>46164</v>
+      </c>
+      <c r="C111" t="s">
+        <v>217</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>111</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46164</v>
+      </c>
+      <c r="C112" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D417EB4-E136-4DC2-BB7D-D63CC609D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2846DBDD-90E4-4EB5-A0F4-AFC5F86A3096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="223">
   <si>
     <t>London</t>
   </si>
@@ -698,6 +698,12 @@
   </si>
   <si>
     <t>Wolverton Townsend</t>
+  </si>
+  <si>
+    <t>The Rowbarge</t>
+  </si>
+  <si>
+    <t>Woolhampton</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1235,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1277,7 +1283,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3074,82 +3080,91 @@
         <v>220</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B113" s="1">
+        <v>46165</v>
+      </c>
+      <c r="C113" t="s">
+        <v>221</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>127</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2846DBDD-90E4-4EB5-A0F4-AFC5F86A3096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993E71EA-5340-4E8B-BF1D-7F364AF596B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21132" windowHeight="8880" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="227">
   <si>
     <t>London</t>
   </si>
@@ -704,6 +704,18 @@
   </si>
   <si>
     <t>Woolhampton</t>
+  </si>
+  <si>
+    <t>The Mill House</t>
+  </si>
+  <si>
+    <t>North Warnborough</t>
+  </si>
+  <si>
+    <t>cw</t>
+  </si>
+  <si>
+    <t>bq</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1247,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1283,7 +1295,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3097,6 +3109,15 @@
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46168</v>
+      </c>
+      <c r="C114" t="s">
+        <v>223</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -4895,10 +4916,16 @@
       <c r="A63" s="8">
         <v>62</v>
       </c>
+      <c r="E63" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>63</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993E71EA-5340-4E8B-BF1D-7F364AF596B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DEDD59-E7F5-4D39-B1B3-D0CE35B441A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="21132" windowHeight="8880" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="230">
   <si>
     <t>London</t>
   </si>
@@ -716,6 +716,15 @@
   </si>
   <si>
     <t>bq</t>
+  </si>
+  <si>
+    <t>The Swan Inn</t>
+  </si>
+  <si>
+    <t>The Royal Oak</t>
+  </si>
+  <si>
+    <t>Ecchinswell</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1256,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1295,7 +1304,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3124,10 +3133,28 @@
       <c r="A115" s="8">
         <v>114</v>
       </c>
+      <c r="B115" s="1">
+        <v>46171</v>
+      </c>
+      <c r="C115" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46171</v>
+      </c>
+      <c r="C116" t="s">
+        <v>228</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DEDD59-E7F5-4D39-B1B3-D0CE35B441A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23B831F-4A7B-4AE8-93D5-646DC3AA9ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -21,21 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="236">
   <si>
     <t>London</t>
   </si>
@@ -725,6 +716,24 @@
   </si>
   <si>
     <t>Ecchinswell</t>
+  </si>
+  <si>
+    <t>Steam Town Brew Co.</t>
+  </si>
+  <si>
+    <t>The Wagon Works</t>
+  </si>
+  <si>
+    <t>The Butcher</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Schiphol</t>
+  </si>
+  <si>
+    <t>nl</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1265,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1280,7 +1289,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1304,7 +1313,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1364,7 +1373,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3101,7 +3110,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>112</v>
       </c>
@@ -3115,7 +3124,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>113</v>
       </c>
@@ -3129,7 +3138,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>114</v>
       </c>
@@ -3143,7 +3152,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>115</v>
       </c>
@@ -3157,62 +3166,83 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B117" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C117" t="s">
+        <v>230</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B118" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C118" t="s">
+        <v>231</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>127</v>
       </c>
@@ -4943,8 +4973,17 @@
       <c r="A63" s="8">
         <v>62</v>
       </c>
+      <c r="B63" s="1">
+        <v>46175</v>
+      </c>
+      <c r="C63" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
       <c r="E63" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -4955,82 +4994,85 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E65" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>79</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23B831F-4A7B-4AE8-93D5-646DC3AA9ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15DD862-AEC1-43BD-AB6A-0C14372D6FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -20,6 +20,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15DD862-AEC1-43BD-AB6A-0C14372D6FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F6D3F4-629C-4B32-BC4C-B84EE6DC8D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="238">
   <si>
     <t>London</t>
   </si>
@@ -743,6 +743,12 @@
   </si>
   <si>
     <t>nl</t>
+  </si>
+  <si>
+    <t>Westpunt</t>
+  </si>
+  <si>
+    <t>Cactus Café</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1304,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1322,7 +1328,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3920,7 +3926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D790B87A-E441-4AAE-B37D-754410287600}">
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -4999,89 +5005,101 @@
       <c r="A64" s="8">
         <v>63</v>
       </c>
+      <c r="B64" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C64" t="s">
+        <v>237</v>
+      </c>
+      <c r="D64" t="s">
+        <v>236</v>
+      </c>
       <c r="E64" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>64</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>79</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F6D3F4-629C-4B32-BC4C-B84EE6DC8D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0488E38C-AA93-4F51-B331-70D06A545A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="241">
   <si>
     <t>London</t>
   </si>
@@ -749,6 +749,15 @@
   </si>
   <si>
     <t>Cactus Café</t>
+  </si>
+  <si>
+    <t>Swinging Old Lady Brewery</t>
+  </si>
+  <si>
+    <t>Willhemstad</t>
+  </si>
+  <si>
+    <t>Yat Sun???</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1313,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1328,7 +1337,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3926,7 +3935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D790B87A-E441-4AAE-B37D-754410287600}">
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -5018,88 +5027,109 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>64</v>
       </c>
-      <c r="F65" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B65" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C65" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>65</v>
       </c>
-      <c r="F66" t="s">
+      <c r="B66" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" t="s">
+        <v>239</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E71" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>79</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0488E38C-AA93-4F51-B331-70D06A545A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B491579-0DA6-409D-9C7D-F9BCB03DBF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="243">
   <si>
     <t>London</t>
   </si>
@@ -758,6 +758,12 @@
   </si>
   <si>
     <t>Yat Sun???</t>
+  </si>
+  <si>
+    <t>One Vibe</t>
+  </si>
+  <si>
+    <t>Bugs Bunny</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1319,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1337,7 +1343,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5065,10 +5071,34 @@
       <c r="A67" s="8">
         <v>66</v>
       </c>
+      <c r="B67" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C67" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" t="s">
+        <v>239</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46184</v>
+      </c>
+      <c r="C68" t="s">
+        <v>241</v>
+      </c>
+      <c r="D68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B491579-0DA6-409D-9C7D-F9BCB03DBF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEBBA8E-451F-4FE8-BF2C-68C59CE07AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="246">
   <si>
     <t>London</t>
   </si>
@@ -757,13 +757,22 @@
     <t>Willhemstad</t>
   </si>
   <si>
-    <t>Yat Sun???</t>
-  </si>
-  <si>
     <t>One Vibe</t>
   </si>
   <si>
     <t>Bugs Bunny</t>
+  </si>
+  <si>
+    <t>Sabor Los Mellos</t>
+  </si>
+  <si>
+    <t>Landhuis Chobolobo</t>
+  </si>
+  <si>
+    <t>La Coco Jambo Favela Bar</t>
+  </si>
+  <si>
+    <t>????</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1343,7 +1352,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5058,7 +5067,7 @@
         <v>46183</v>
       </c>
       <c r="C66" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D66" t="s">
         <v>239</v>
@@ -5075,7 +5084,7 @@
         <v>46184</v>
       </c>
       <c r="C67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D67" t="s">
         <v>239</v>
@@ -5092,7 +5101,7 @@
         <v>46184</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
         <v>239</v>
@@ -5105,23 +5114,59 @@
       <c r="A69" s="8">
         <v>68</v>
       </c>
+      <c r="B69" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C69" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>69</v>
       </c>
+      <c r="B70" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>70</v>
       </c>
+      <c r="B71" s="1">
+        <v>46185</v>
+      </c>
+      <c r="C71" t="s">
+        <v>245</v>
+      </c>
+      <c r="D71" t="s">
+        <v>239</v>
+      </c>
       <c r="E71" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>71</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEBBA8E-451F-4FE8-BF2C-68C59CE07AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722CB61-DA5D-4239-B958-BE2A36206693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="251">
   <si>
     <t>London</t>
   </si>
@@ -773,6 +773,21 @@
   </si>
   <si>
     <t>????</t>
+  </si>
+  <si>
+    <t>El Mundo</t>
+  </si>
+  <si>
+    <t>Kralendijk</t>
+  </si>
+  <si>
+    <t>Bonaire Blond Brewery</t>
+  </si>
+  <si>
+    <t>The Bucket Bonaire</t>
+  </si>
+  <si>
+    <t>Kanti Awa</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1343,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1352,7 +1367,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5165,6 +5180,15 @@
       <c r="A72" s="8">
         <v>71</v>
       </c>
+      <c r="B72" s="1">
+        <v>46373</v>
+      </c>
+      <c r="C72" t="s">
+        <v>246</v>
+      </c>
+      <c r="D72" t="s">
+        <v>247</v>
+      </c>
       <c r="E72" s="2" t="s">
         <v>226</v>
       </c>
@@ -5173,15 +5197,51 @@
       <c r="A73" s="8">
         <v>72</v>
       </c>
+      <c r="B73" s="1">
+        <v>46373</v>
+      </c>
+      <c r="C73" t="s">
+        <v>248</v>
+      </c>
+      <c r="D73" t="s">
+        <v>247</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>73</v>
       </c>
+      <c r="B74" s="1">
+        <v>46373</v>
+      </c>
+      <c r="C74" t="s">
+        <v>249</v>
+      </c>
+      <c r="D74" t="s">
+        <v>247</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46373</v>
+      </c>
+      <c r="C75" t="s">
+        <v>250</v>
+      </c>
+      <c r="D75" t="s">
+        <v>247</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722CB61-DA5D-4239-B958-BE2A36206693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C748C33C-AC0F-4530-B5A7-AFD61F59E0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="253">
   <si>
     <t>London</t>
   </si>
@@ -788,6 +788,12 @@
   </si>
   <si>
     <t>Kanti Awa</t>
+  </si>
+  <si>
+    <t>Eden Beach Bar</t>
+  </si>
+  <si>
+    <t>Hato</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1349,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1367,7 +1373,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5248,6 +5254,18 @@
       <c r="A76" s="8">
         <v>75</v>
       </c>
+      <c r="B76" s="1">
+        <v>46376</v>
+      </c>
+      <c r="C76" t="s">
+        <v>251</v>
+      </c>
+      <c r="D76" t="s">
+        <v>252</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C748C33C-AC0F-4530-B5A7-AFD61F59E0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C71AF2-CE13-472C-B0CE-A85F58D13B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="254">
   <si>
     <t>London</t>
   </si>
@@ -794,6 +794,9 @@
   </si>
   <si>
     <t>Hato</t>
+  </si>
+  <si>
+    <t>Breeze 'n Bites</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1352,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1373,7 +1376,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5187,7 +5190,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1">
-        <v>46373</v>
+        <v>46190</v>
       </c>
       <c r="C72" t="s">
         <v>246</v>
@@ -5204,7 +5207,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1">
-        <v>46373</v>
+        <v>46190</v>
       </c>
       <c r="C73" t="s">
         <v>248</v>
@@ -5221,7 +5224,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1">
-        <v>46373</v>
+        <v>46190</v>
       </c>
       <c r="C74" t="s">
         <v>249</v>
@@ -5238,7 +5241,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1">
-        <v>46373</v>
+        <v>46190</v>
       </c>
       <c r="C75" t="s">
         <v>250</v>
@@ -5255,7 +5258,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1">
-        <v>46376</v>
+        <v>46192</v>
       </c>
       <c r="C76" t="s">
         <v>251</v>
@@ -5270,6 +5273,18 @@
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>76</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C77" t="s">
+        <v>253</v>
+      </c>
+      <c r="D77" t="s">
+        <v>252</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C71AF2-CE13-472C-B0CE-A85F58D13B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A990EF-E117-437F-B719-7FEB97B1026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="256">
   <si>
     <t>London</t>
   </si>
@@ -797,6 +797,12 @@
   </si>
   <si>
     <t>Breeze 'n Bites</t>
+  </si>
+  <si>
+    <t>Het Consulaat</t>
+  </si>
+  <si>
+    <t>Harbour Village</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1358,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1376,7 +1382,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5291,10 +5297,34 @@
       <c r="A78" s="8">
         <v>77</v>
       </c>
+      <c r="B78" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C78" t="s">
+        <v>254</v>
+      </c>
+      <c r="D78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>78</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C79" t="s">
+        <v>255</v>
+      </c>
+      <c r="D79" t="s">
+        <v>252</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A990EF-E117-437F-B719-7FEB97B1026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E799FE-B8A3-4302-B758-0644F44EB2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -802,7 +802,7 @@
     <t>Het Consulaat</t>
   </si>
   <si>
-    <t>Harbour Village</t>
+    <t>The Harbour</t>
   </si>
 </sst>
 </file>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E799FE-B8A3-4302-B758-0644F44EB2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B8ECA-0FC3-4257-A3E2-D4D0942F56E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="257">
   <si>
     <t>London</t>
   </si>
@@ -803,6 +803,9 @@
   </si>
   <si>
     <t>The Harbour</t>
+  </si>
+  <si>
+    <t>gb</t>
   </si>
 </sst>
 </file>
@@ -921,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -959,6 +962,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1281,7 +1290,7 @@
     <col min="2" max="2" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="8.88671875" style="17"/>
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="5" style="3" customWidth="1"/>
   </cols>
@@ -1297,7 +1306,7 @@
       <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6"/>
+      <c r="E1" s="16"/>
       <c r="F1" s="4"/>
       <c r="G1" s="7"/>
     </row>
@@ -1314,6 +1323,9 @@
       <c r="D2" t="s">
         <v>0</v>
       </c>
+      <c r="E2" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="G2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1329,6 +1341,9 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
+      <c r="E3" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
@@ -1350,7 +1365,7 @@
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -1374,7 +1389,7 @@
       <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F5" s="11" t="s">
@@ -1398,7 +1413,9 @@
       <c r="D6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E6"/>
+      <c r="E6" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12"/>
     </row>
@@ -1415,8 +1432,8 @@
       <c r="D7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E7" t="s">
-        <v>132</v>
+      <c r="E7" s="17" t="s">
+        <v>256</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12"/>
@@ -1434,7 +1451,7 @@
       <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -1442,7 +1459,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1458,7 +1475,9 @@
       <c r="D9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E9"/>
+      <c r="E9" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F9" s="14"/>
       <c r="G9" s="15"/>
     </row>
@@ -1475,7 +1494,7 @@
       <c r="D10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1487,12 +1506,14 @@
         <v>46088</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E11"/>
+      <c r="E11" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
@@ -1502,13 +1523,13 @@
         <v>46088</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E12" t="s">
-        <v>132</v>
+      <c r="E12" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1524,7 +1545,7 @@
       <c r="D13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1541,7 +1562,9 @@
       <c r="D14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E14"/>
+      <c r="E14" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
@@ -1556,7 +1579,9 @@
       <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15"/>
+      <c r="E15" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
@@ -1571,7 +1596,9 @@
       <c r="D16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E16"/>
+      <c r="E16" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16"/>
     </row>
@@ -1588,7 +1615,9 @@
       <c r="D17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E17"/>
+      <c r="E17" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F17" s="3"/>
       <c r="G17"/>
     </row>
@@ -1605,7 +1634,9 @@
       <c r="D18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E18"/>
+      <c r="E18" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18"/>
     </row>
@@ -1622,7 +1653,9 @@
       <c r="D19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19"/>
+      <c r="E19" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F19" s="3"/>
       <c r="G19"/>
     </row>
@@ -1639,7 +1672,9 @@
       <c r="D20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E20"/>
+      <c r="E20" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F20" s="3"/>
       <c r="G20"/>
     </row>
@@ -1656,7 +1691,9 @@
       <c r="D21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E21"/>
+      <c r="E21" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F21" s="3"/>
       <c r="G21"/>
     </row>
@@ -1673,7 +1710,9 @@
       <c r="D22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E22"/>
+      <c r="E22" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F22" s="3"/>
       <c r="G22"/>
     </row>
@@ -1690,7 +1729,9 @@
       <c r="D23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E23"/>
+      <c r="E23" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23"/>
     </row>
@@ -1707,7 +1748,7 @@
       <c r="D24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F24" s="3"/>
@@ -1726,7 +1767,9 @@
       <c r="D25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E25"/>
+      <c r="E25" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25"/>
     </row>
@@ -1743,7 +1786,9 @@
       <c r="D26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E26"/>
+      <c r="E26" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F26" s="3"/>
       <c r="G26"/>
     </row>
@@ -1760,7 +1805,9 @@
       <c r="D27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E27"/>
+      <c r="E27" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27"/>
     </row>
@@ -1777,7 +1824,9 @@
       <c r="D28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E28"/>
+      <c r="E28" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F28" s="3"/>
       <c r="G28"/>
     </row>
@@ -1794,7 +1843,9 @@
       <c r="D29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E29"/>
+      <c r="E29" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F29" s="3"/>
       <c r="G29"/>
     </row>
@@ -1811,7 +1862,9 @@
       <c r="D30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E30"/>
+      <c r="E30" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F30" s="3"/>
       <c r="G30"/>
     </row>
@@ -1828,7 +1881,9 @@
       <c r="D31" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E31"/>
+      <c r="E31" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F31" s="3"/>
       <c r="G31"/>
     </row>
@@ -1845,7 +1900,9 @@
       <c r="D32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E32"/>
+      <c r="E32" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F32" s="3"/>
       <c r="G32"/>
     </row>
@@ -1862,7 +1919,9 @@
       <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E33"/>
+      <c r="E33" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F33" s="3"/>
       <c r="G33"/>
     </row>
@@ -1879,7 +1938,9 @@
       <c r="D34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E34"/>
+      <c r="E34" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F34" s="3"/>
       <c r="G34"/>
     </row>
@@ -1896,7 +1957,9 @@
       <c r="D35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E35"/>
+      <c r="E35" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F35" s="3"/>
       <c r="G35"/>
     </row>
@@ -1913,7 +1976,9 @@
       <c r="D36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E36"/>
+      <c r="E36" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F36" s="3"/>
       <c r="G36"/>
     </row>
@@ -1930,7 +1995,9 @@
       <c r="D37" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E37"/>
+      <c r="E37" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F37" s="3"/>
       <c r="G37"/>
     </row>
@@ -1947,7 +2014,9 @@
       <c r="D38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E38"/>
+      <c r="E38" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F38" s="3"/>
       <c r="G38"/>
     </row>
@@ -1964,7 +2033,9 @@
       <c r="D39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E39"/>
+      <c r="E39" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F39" s="3"/>
       <c r="G39"/>
     </row>
@@ -1981,7 +2052,9 @@
       <c r="D40" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E40"/>
+      <c r="E40" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F40" s="3"/>
       <c r="G40"/>
     </row>
@@ -1998,7 +2071,9 @@
       <c r="D41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E41"/>
+      <c r="E41" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F41" s="3"/>
       <c r="G41"/>
     </row>
@@ -2015,7 +2090,9 @@
       <c r="D42" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E42"/>
+      <c r="E42" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F42" s="3"/>
       <c r="G42"/>
     </row>
@@ -2032,7 +2109,9 @@
       <c r="D43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E43"/>
+      <c r="E43" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F43" s="3"/>
       <c r="G43"/>
     </row>
@@ -2049,7 +2128,7 @@
       <c r="D44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F44" s="3"/>
@@ -2068,7 +2147,9 @@
       <c r="D45" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E45"/>
+      <c r="E45" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F45" s="3"/>
       <c r="G45"/>
     </row>
@@ -2085,7 +2166,9 @@
       <c r="D46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E46"/>
+      <c r="E46" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F46" s="3"/>
       <c r="G46"/>
     </row>
@@ -2102,7 +2185,9 @@
       <c r="D47" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E47"/>
+      <c r="E47" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F47" s="3"/>
       <c r="G47"/>
     </row>
@@ -2119,7 +2204,9 @@
       <c r="D48" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E48"/>
+      <c r="E48" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F48" s="3"/>
       <c r="G48"/>
     </row>
@@ -2136,7 +2223,9 @@
       <c r="D49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E49"/>
+      <c r="E49" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F49" s="3"/>
       <c r="G49"/>
     </row>
@@ -2153,7 +2242,7 @@
       <c r="D50" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F50" s="3"/>
@@ -2172,7 +2261,7 @@
       <c r="D51" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F51" s="3"/>
@@ -2191,7 +2280,9 @@
       <c r="D52" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E52"/>
+      <c r="E52" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F52" s="3"/>
       <c r="G52"/>
     </row>
@@ -2208,7 +2299,9 @@
       <c r="D53" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E53"/>
+      <c r="E53" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53"/>
     </row>
@@ -2225,7 +2318,9 @@
       <c r="D54" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E54"/>
+      <c r="E54" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F54" s="3"/>
       <c r="G54"/>
     </row>
@@ -2242,7 +2337,9 @@
       <c r="D55" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E55"/>
+      <c r="E55" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F55" s="3"/>
       <c r="G55"/>
     </row>
@@ -2259,7 +2356,9 @@
       <c r="D56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E56"/>
+      <c r="E56" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F56" s="3"/>
       <c r="G56"/>
     </row>
@@ -2276,7 +2375,9 @@
       <c r="D57" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E57"/>
+      <c r="E57" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F57" s="3"/>
       <c r="G57"/>
     </row>
@@ -2293,7 +2394,7 @@
       <c r="D58" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F58" s="3"/>
@@ -2312,7 +2413,9 @@
       <c r="D59" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E59"/>
+      <c r="E59" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F59" s="3"/>
       <c r="G59"/>
     </row>
@@ -2329,7 +2432,9 @@
       <c r="D60" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E60"/>
+      <c r="E60" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F60" s="3"/>
       <c r="G60"/>
     </row>
@@ -2346,7 +2451,9 @@
       <c r="D61" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E61"/>
+      <c r="E61" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F61" s="3"/>
       <c r="G61"/>
     </row>
@@ -2363,7 +2470,9 @@
       <c r="D62" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E62"/>
+      <c r="E62" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F62" s="3"/>
       <c r="G62"/>
     </row>
@@ -2380,7 +2489,9 @@
       <c r="D63" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E63"/>
+      <c r="E63" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F63" s="3"/>
       <c r="G63"/>
     </row>
@@ -2397,7 +2508,9 @@
       <c r="D64" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E64"/>
+      <c r="E64" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F64" s="3"/>
       <c r="G64"/>
     </row>
@@ -2414,7 +2527,9 @@
       <c r="D65" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E65"/>
+      <c r="E65" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F65" s="3"/>
       <c r="G65"/>
     </row>
@@ -2431,7 +2546,9 @@
       <c r="D66" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E66"/>
+      <c r="E66" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F66" s="3"/>
       <c r="G66"/>
     </row>
@@ -2448,7 +2565,7 @@
       <c r="D67" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F67" s="3"/>
@@ -2467,7 +2584,9 @@
       <c r="D68" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E68"/>
+      <c r="E68" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F68" s="3"/>
       <c r="G68"/>
     </row>
@@ -2484,7 +2603,9 @@
       <c r="D69" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E69"/>
+      <c r="E69" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F69" s="3"/>
       <c r="G69"/>
     </row>
@@ -2501,7 +2622,9 @@
       <c r="D70" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E70"/>
+      <c r="E70" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F70" s="3"/>
       <c r="G70"/>
     </row>
@@ -2518,7 +2641,9 @@
       <c r="D71" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E71"/>
+      <c r="E71" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F71" s="3"/>
       <c r="G71"/>
     </row>
@@ -2535,7 +2660,9 @@
       <c r="D72" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E72"/>
+      <c r="E72" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F72" s="3"/>
       <c r="G72"/>
     </row>
@@ -2552,7 +2679,9 @@
       <c r="D73" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E73"/>
+      <c r="E73" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F73" s="3"/>
       <c r="G73"/>
     </row>
@@ -2569,7 +2698,9 @@
       <c r="D74" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E74"/>
+      <c r="E74" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F74" s="3"/>
       <c r="G74"/>
     </row>
@@ -2586,7 +2717,9 @@
       <c r="D75" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E75"/>
+      <c r="E75" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F75" s="3"/>
       <c r="G75"/>
     </row>
@@ -2603,7 +2736,9 @@
       <c r="D76" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E76"/>
+      <c r="E76" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F76" s="3"/>
       <c r="G76"/>
     </row>
@@ -2620,7 +2755,9 @@
       <c r="D77" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E77"/>
+      <c r="E77" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F77" s="3"/>
       <c r="G77"/>
     </row>
@@ -2637,7 +2774,7 @@
       <c r="D78" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F78" s="3"/>
@@ -2656,7 +2793,9 @@
       <c r="D79" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E79"/>
+      <c r="E79" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F79" s="3"/>
       <c r="G79"/>
     </row>
@@ -2673,7 +2812,9 @@
       <c r="D80" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E80"/>
+      <c r="E80" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F80" s="3"/>
       <c r="G80"/>
     </row>
@@ -2690,7 +2831,9 @@
       <c r="D81" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E81"/>
+      <c r="E81" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F81" s="3"/>
       <c r="G81"/>
     </row>
@@ -2707,7 +2850,7 @@
       <c r="D82" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F82" s="3"/>
@@ -2726,7 +2869,9 @@
       <c r="D83" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E83"/>
+      <c r="E83" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F83" s="3"/>
       <c r="G83"/>
     </row>
@@ -2743,7 +2888,9 @@
       <c r="D84" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E84"/>
+      <c r="E84" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F84" s="3"/>
       <c r="G84"/>
     </row>
@@ -2760,7 +2907,9 @@
       <c r="D85" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E85"/>
+      <c r="E85" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F85" s="3"/>
       <c r="G85"/>
     </row>
@@ -2777,7 +2926,9 @@
       <c r="D86" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E86"/>
+      <c r="E86" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F86" s="3"/>
       <c r="G86"/>
     </row>
@@ -2794,6 +2945,9 @@
       <c r="D87" s="2" t="s">
         <v>140</v>
       </c>
+      <c r="E87" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F87" s="3"/>
       <c r="G87"/>
     </row>
@@ -2810,6 +2964,9 @@
       <c r="D88" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="E88" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F88" s="3"/>
       <c r="G88"/>
     </row>
@@ -2826,6 +2983,9 @@
       <c r="D89" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="E89" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F89" s="3"/>
       <c r="G89"/>
     </row>
@@ -2842,6 +3002,9 @@
       <c r="D90" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="E90" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F90" s="3"/>
       <c r="G90"/>
     </row>
@@ -2858,6 +3021,9 @@
       <c r="D91" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="E91" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F91" s="3"/>
       <c r="G91"/>
     </row>
@@ -2874,6 +3040,9 @@
       <c r="D92" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="E92" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F92" s="3"/>
       <c r="G92"/>
     </row>
@@ -2890,7 +3059,7 @@
       <c r="D93" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F93" s="3"/>
@@ -2909,6 +3078,9 @@
       <c r="D94" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E94" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F94" s="3"/>
       <c r="G94"/>
     </row>
@@ -2925,6 +3097,9 @@
       <c r="D95" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E95" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F95" s="3"/>
       <c r="G95"/>
     </row>
@@ -2941,6 +3116,9 @@
       <c r="D96" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E96" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F96" s="3"/>
       <c r="G96"/>
     </row>
@@ -2957,6 +3135,9 @@
       <c r="D97" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E97" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="F97" s="3"/>
       <c r="G97"/>
     </row>
@@ -2973,6 +3154,9 @@
       <c r="D98" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E98" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
@@ -2987,6 +3171,9 @@
       <c r="D99" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E99" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
@@ -3001,6 +3188,9 @@
       <c r="D100" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E100" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
@@ -3015,6 +3205,9 @@
       <c r="D101" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E101" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
@@ -3029,6 +3222,9 @@
       <c r="D102" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E102" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
@@ -3043,6 +3239,9 @@
       <c r="D103" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E103" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
@@ -3057,6 +3256,9 @@
       <c r="D104" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E104" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
@@ -3071,7 +3273,7 @@
       <c r="D105" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3088,6 +3290,9 @@
       <c r="D106" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E106" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
@@ -3102,6 +3307,9 @@
       <c r="D107" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="E107" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
@@ -3116,6 +3324,9 @@
       <c r="D108" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="E108" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
@@ -3130,7 +3341,7 @@
       <c r="D109" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3147,7 +3358,7 @@
       <c r="D110" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3164,6 +3375,9 @@
       <c r="D111" s="2" t="s">
         <v>218</v>
       </c>
+      <c r="E111" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
@@ -3178,6 +3392,9 @@
       <c r="D112" s="2" t="s">
         <v>220</v>
       </c>
+      <c r="E112" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
@@ -3192,6 +3409,9 @@
       <c r="D113" s="2" t="s">
         <v>222</v>
       </c>
+      <c r="E113" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
@@ -3206,6 +3426,9 @@
       <c r="D114" s="2" t="s">
         <v>224</v>
       </c>
+      <c r="E114" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
@@ -3220,6 +3443,9 @@
       <c r="D115" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="E115" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
@@ -3234,6 +3460,9 @@
       <c r="D116" s="2" t="s">
         <v>229</v>
       </c>
+      <c r="E116" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
@@ -3248,6 +3477,9 @@
       <c r="D117" s="2" t="s">
         <v>233</v>
       </c>
+      <c r="E117" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
@@ -3262,7 +3494,7 @@
       <c r="D118" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3556,83 +3788,82 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>183</v>
       </c>
-      <c r="E184"/>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>191</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B8ECA-0FC3-4257-A3E2-D4D0942F56E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0858A61-E7EF-4DD6-B1EF-0B09CC84A9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="260">
   <si>
     <t>London</t>
   </si>
@@ -806,6 +806,15 @@
   </si>
   <si>
     <t>gb</t>
+  </si>
+  <si>
+    <t>Sherborne St John</t>
+  </si>
+  <si>
+    <t>The Crown</t>
+  </si>
+  <si>
+    <t>The George &amp; Horn</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1358,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1397,7 +1406,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3502,15 +3511,51 @@
       <c r="A119" s="8">
         <v>118</v>
       </c>
+      <c r="B119" s="1">
+        <v>46214</v>
+      </c>
+      <c r="C119" t="s">
+        <v>227</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E119" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>119</v>
       </c>
+      <c r="B120" s="1">
+        <v>46214</v>
+      </c>
+      <c r="C120" t="s">
+        <v>258</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E120" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>120</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46214</v>
+      </c>
+      <c r="C121" t="s">
+        <v>259</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E121" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0858A61-E7EF-4DD6-B1EF-0B09CC84A9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AD6FE6-2F36-4276-B549-9761890FAEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="264">
   <si>
     <t>London</t>
   </si>
@@ -815,6 +815,18 @@
   </si>
   <si>
     <t>The George &amp; Horn</t>
+  </si>
+  <si>
+    <t>The Carpenters Arms</t>
+  </si>
+  <si>
+    <t>Burghclere</t>
+  </si>
+  <si>
+    <t>The Carnarvon Arms</t>
+  </si>
+  <si>
+    <t>Whitway</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1370,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1406,7 +1418,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3562,10 +3574,34 @@
       <c r="A122" s="8">
         <v>121</v>
       </c>
+      <c r="B122" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C122" t="s">
+        <v>260</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E122" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>122</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C123" t="s">
+        <v>262</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E123" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AD6FE6-2F36-4276-B549-9761890FAEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E19B36-4C92-472C-AF1E-D951065632D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="266">
   <si>
     <t>London</t>
   </si>
@@ -827,6 +827,12 @@
   </si>
   <si>
     <t>Whitway</t>
+  </si>
+  <si>
+    <t>The Bricklayers Arms</t>
+  </si>
+  <si>
+    <t>Parched</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1376,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1418,7 +1424,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3608,10 +3614,34 @@
       <c r="A124" s="8">
         <v>123</v>
       </c>
+      <c r="B124" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C124" t="s">
+        <v>264</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E124" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>124</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C125" t="s">
+        <v>265</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E125" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E19B36-4C92-472C-AF1E-D951065632D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191B160C-9B25-4568-B563-3DD4BD4C5ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="271">
   <si>
     <t>London</t>
   </si>
@@ -833,6 +833,21 @@
   </si>
   <si>
     <t>Parched</t>
+  </si>
+  <si>
+    <t>The Black Swan</t>
+  </si>
+  <si>
+    <t>The Swan Taphouse</t>
+  </si>
+  <si>
+    <t>The Coracle Micropub</t>
+  </si>
+  <si>
+    <t>Jackfield</t>
+  </si>
+  <si>
+    <t>Ironbridge</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1391,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1424,7 +1439,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3648,15 +3663,51 @@
       <c r="A126" s="8">
         <v>125</v>
       </c>
+      <c r="B126" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C126" t="s">
+        <v>266</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>126</v>
       </c>
+      <c r="B127" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C127" t="s">
+        <v>267</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E127" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>127</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C128" t="s">
+        <v>268</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191B160C-9B25-4568-B563-3DD4BD4C5ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458395E8-C229-4DEE-85AF-76EC9C29452F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="275">
   <si>
     <t>London</t>
   </si>
@@ -848,6 +848,18 @@
   </si>
   <si>
     <t>Ironbridge</t>
+  </si>
+  <si>
+    <t>The Woodbridge Inn</t>
+  </si>
+  <si>
+    <t>The Brewery Inn</t>
+  </si>
+  <si>
+    <t>The Water Rat Inn</t>
+  </si>
+  <si>
+    <t>Coalport</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1403,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1439,7 +1451,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3710,82 +3722,118 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B129" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C129" t="s">
+        <v>271</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C130" t="s">
+        <v>272</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E130" s="17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C131" t="s">
+        <v>273</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>143</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458395E8-C229-4DEE-85AF-76EC9C29452F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA024C-E766-406D-B7C2-C087261CD632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="279">
   <si>
     <t>London</t>
   </si>
@@ -860,6 +860,18 @@
   </si>
   <si>
     <t>Coalport</t>
+  </si>
+  <si>
+    <t>The Three Merry Lads</t>
+  </si>
+  <si>
+    <t>Rising Sun Inn</t>
+  </si>
+  <si>
+    <t>The Fargate</t>
+  </si>
+  <si>
+    <t>Dog &amp; Partridge</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1415,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1451,7 +1463,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3777,26 +3789,75 @@
       <c r="A132" s="8">
         <v>131</v>
       </c>
+      <c r="B132" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C132" t="s">
+        <v>275</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E132" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>132</v>
       </c>
+      <c r="B133" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C133" t="s">
+        <v>276</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E133" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>133</v>
       </c>
+      <c r="B134" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C134" t="s">
+        <v>277</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E134" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>134</v>
       </c>
+      <c r="B135" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C135" t="s">
+        <v>278</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E135" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>135</v>
       </c>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA024C-E766-406D-B7C2-C087261CD632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863F6931-20AE-41CF-B9D8-CF428F66D1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="285">
   <si>
     <t>London</t>
   </si>
@@ -872,6 +872,24 @@
   </si>
   <si>
     <t>Dog &amp; Partridge</t>
+  </si>
+  <si>
+    <t>Peterborough</t>
+  </si>
+  <si>
+    <t>Charters Bar</t>
+  </si>
+  <si>
+    <t>Queen's Head</t>
+  </si>
+  <si>
+    <t>The Draper's Arms</t>
+  </si>
+  <si>
+    <t>The Brewery Tap</t>
+  </si>
+  <si>
+    <t>The Bumble Inn</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1373,7 @@
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="17"/>
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="5" style="3" customWidth="1"/>
@@ -1369,7 +1387,7 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="16"/>
@@ -1386,7 +1404,7 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="17" t="s">
@@ -1404,7 +1422,7 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="17" t="s">
@@ -1415,7 +1433,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1428,7 +1446,7 @@
       <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -1452,7 +1470,7 @@
       <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -1463,7 +1481,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1476,7 +1494,7 @@
       <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -1495,7 +1513,7 @@
       <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="17" t="s">
@@ -1514,7 +1532,7 @@
       <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="17" t="s">
         <v>41</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -1525,7 +1543,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1538,7 +1556,7 @@
       <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="17" t="s">
         <v>43</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -1557,7 +1575,7 @@
       <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="17" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -1574,7 +1592,7 @@
       <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="17" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -1591,7 +1609,7 @@
       <c r="C12" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="17" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -1608,7 +1626,7 @@
       <c r="C13" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -1625,7 +1643,7 @@
       <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -1642,7 +1660,7 @@
       <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -1659,7 +1677,7 @@
       <c r="C16" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -1678,7 +1696,7 @@
       <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -1697,7 +1715,7 @@
       <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -1716,7 +1734,7 @@
       <c r="C19" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -1735,7 +1753,7 @@
       <c r="C20" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -1754,7 +1772,7 @@
       <c r="C21" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -1773,7 +1791,7 @@
       <c r="C22" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -1792,7 +1810,7 @@
       <c r="C23" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -1811,7 +1829,7 @@
       <c r="C24" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -1830,7 +1848,7 @@
       <c r="C25" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="17" t="s">
         <v>62</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -1849,7 +1867,7 @@
       <c r="C26" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="17" t="s">
         <v>62</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -1868,7 +1886,7 @@
       <c r="C27" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="17" t="s">
         <v>62</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -1887,7 +1905,7 @@
       <c r="C28" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="17" t="s">
         <v>62</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -1906,7 +1924,7 @@
       <c r="C29" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="17" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -1925,7 +1943,7 @@
       <c r="C30" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -1944,7 +1962,7 @@
       <c r="C31" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -1963,7 +1981,7 @@
       <c r="C32" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -1982,7 +2000,7 @@
       <c r="C33" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E33" s="17" t="s">
@@ -2001,7 +2019,7 @@
       <c r="C34" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -2020,7 +2038,7 @@
       <c r="C35" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E35" s="17" t="s">
@@ -2039,7 +2057,7 @@
       <c r="C36" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="17" t="s">
         <v>74</v>
       </c>
       <c r="E36" s="17" t="s">
@@ -2058,7 +2076,7 @@
       <c r="C37" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -2077,7 +2095,7 @@
       <c r="C38" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E38" s="17" t="s">
@@ -2096,7 +2114,7 @@
       <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E39" s="17" t="s">
@@ -2115,7 +2133,7 @@
       <c r="C40" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E40" s="17" t="s">
@@ -2134,7 +2152,7 @@
       <c r="C41" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E41" s="17" t="s">
@@ -2153,7 +2171,7 @@
       <c r="C42" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E42" s="17" t="s">
@@ -2172,7 +2190,7 @@
       <c r="C43" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E43" s="17" t="s">
@@ -2191,7 +2209,7 @@
       <c r="C44" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E44" s="17" t="s">
@@ -2210,7 +2228,7 @@
       <c r="C45" t="s">
         <v>84</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E45" s="17" t="s">
@@ -2229,7 +2247,7 @@
       <c r="C46" t="s">
         <v>85</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E46" s="17" t="s">
@@ -2248,7 +2266,7 @@
       <c r="C47" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E47" s="17" t="s">
@@ -2267,7 +2285,7 @@
       <c r="C48" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E48" s="17" t="s">
@@ -2286,7 +2304,7 @@
       <c r="C49" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E49" s="17" t="s">
@@ -2305,7 +2323,7 @@
       <c r="C50" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="17" t="s">
         <v>91</v>
       </c>
       <c r="E50" s="17" t="s">
@@ -2324,7 +2342,7 @@
       <c r="C51" t="s">
         <v>92</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E51" s="17" t="s">
@@ -2343,7 +2361,7 @@
       <c r="C52" t="s">
         <v>94</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E52" s="17" t="s">
@@ -2362,7 +2380,7 @@
       <c r="C53" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E53" s="17" t="s">
@@ -2381,7 +2399,7 @@
       <c r="C54" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E54" s="17" t="s">
@@ -2400,7 +2418,7 @@
       <c r="C55" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E55" s="17" t="s">
@@ -2419,7 +2437,7 @@
       <c r="C56" t="s">
         <v>98</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E56" s="17" t="s">
@@ -2438,7 +2456,7 @@
       <c r="C57" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E57" s="17" t="s">
@@ -2457,7 +2475,7 @@
       <c r="C58" t="s">
         <v>100</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E58" s="17" t="s">
@@ -2476,7 +2494,7 @@
       <c r="C59" t="s">
         <v>101</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E59" s="17" t="s">
@@ -2495,7 +2513,7 @@
       <c r="C60" t="s">
         <v>102</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E60" s="17" t="s">
@@ -2514,7 +2532,7 @@
       <c r="C61" t="s">
         <v>103</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E61" s="17" t="s">
@@ -2533,7 +2551,7 @@
       <c r="C62" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E62" s="17" t="s">
@@ -2552,7 +2570,7 @@
       <c r="C63" t="s">
         <v>105</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E63" s="17" t="s">
@@ -2571,7 +2589,7 @@
       <c r="C64" t="s">
         <v>106</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E64" s="17" t="s">
@@ -2590,7 +2608,7 @@
       <c r="C65" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="17" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="17" t="s">
@@ -2609,7 +2627,7 @@
       <c r="C66" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="17" t="s">
         <v>108</v>
       </c>
       <c r="E66" s="17" t="s">
@@ -2628,7 +2646,7 @@
       <c r="C67" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E67" s="17" t="s">
@@ -2647,7 +2665,7 @@
       <c r="C68" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E68" s="17" t="s">
@@ -2666,7 +2684,7 @@
       <c r="C69" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E69" s="17" t="s">
@@ -2685,7 +2703,7 @@
       <c r="C70" t="s">
         <v>114</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E70" s="17" t="s">
@@ -2704,7 +2722,7 @@
       <c r="C71" t="s">
         <v>115</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E71" s="17" t="s">
@@ -2723,7 +2741,7 @@
       <c r="C72" t="s">
         <v>116</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E72" s="17" t="s">
@@ -2742,7 +2760,7 @@
       <c r="C73" t="s">
         <v>117</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E73" s="17" t="s">
@@ -2761,7 +2779,7 @@
       <c r="C74" t="s">
         <v>118</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E74" s="17" t="s">
@@ -2780,7 +2798,7 @@
       <c r="C75" t="s">
         <v>119</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E75" s="17" t="s">
@@ -2799,7 +2817,7 @@
       <c r="C76" t="s">
         <v>120</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E76" s="17" t="s">
@@ -2818,7 +2836,7 @@
       <c r="C77" t="s">
         <v>121</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E77" s="17" t="s">
@@ -2837,7 +2855,7 @@
       <c r="C78" t="s">
         <v>122</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E78" s="17" t="s">
@@ -2856,7 +2874,7 @@
       <c r="C79" t="s">
         <v>123</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E79" s="17" t="s">
@@ -2875,7 +2893,7 @@
       <c r="C80" t="s">
         <v>124</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E80" s="17" t="s">
@@ -2894,7 +2912,7 @@
       <c r="C81" t="s">
         <v>125</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E81" s="17" t="s">
@@ -2913,7 +2931,7 @@
       <c r="C82" t="s">
         <v>126</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E82" s="17" t="s">
@@ -2932,7 +2950,7 @@
       <c r="C83" t="s">
         <v>127</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E83" s="17" t="s">
@@ -2951,7 +2969,7 @@
       <c r="C84" t="s">
         <v>128</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="17" t="s">
         <v>111</v>
       </c>
       <c r="E84" s="17" t="s">
@@ -2970,7 +2988,7 @@
       <c r="C85" t="s">
         <v>129</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="17" t="s">
         <v>130</v>
       </c>
       <c r="E85" s="17" t="s">
@@ -2989,7 +3007,7 @@
       <c r="C86" t="s">
         <v>131</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="17" t="s">
         <v>130</v>
       </c>
       <c r="E86" s="17" t="s">
@@ -3008,7 +3026,7 @@
       <c r="C87" t="s">
         <v>139</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="17" t="s">
         <v>140</v>
       </c>
       <c r="E87" s="17" t="s">
@@ -3027,7 +3045,7 @@
       <c r="C88" t="s">
         <v>133</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E88" s="17" t="s">
@@ -3046,7 +3064,7 @@
       <c r="C89" t="s">
         <v>134</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E89" s="17" t="s">
@@ -3065,7 +3083,7 @@
       <c r="C90" t="s">
         <v>135</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E90" s="17" t="s">
@@ -3084,7 +3102,7 @@
       <c r="C91" t="s">
         <v>136</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E91" s="17" t="s">
@@ -3103,7 +3121,7 @@
       <c r="C92" t="s">
         <v>137</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="17" t="s">
         <v>0</v>
       </c>
       <c r="E92" s="17" t="s">
@@ -3122,7 +3140,7 @@
       <c r="C93" t="s">
         <v>138</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="17" t="s">
         <v>140</v>
       </c>
       <c r="E93" s="17" t="s">
@@ -3141,7 +3159,7 @@
       <c r="C94" t="s">
         <v>144</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E94" s="17" t="s">
@@ -3160,7 +3178,7 @@
       <c r="C95" t="s">
         <v>145</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E95" s="17" t="s">
@@ -3179,7 +3197,7 @@
       <c r="C96" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E96" s="17" t="s">
@@ -3198,7 +3216,7 @@
       <c r="C97" t="s">
         <v>147</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E97" s="17" t="s">
@@ -3217,7 +3235,7 @@
       <c r="C98" t="s">
         <v>148</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E98" s="17" t="s">
@@ -3234,7 +3252,7 @@
       <c r="C99" t="s">
         <v>149</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E99" s="17" t="s">
@@ -3251,7 +3269,7 @@
       <c r="C100" t="s">
         <v>150</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E100" s="17" t="s">
@@ -3268,7 +3286,7 @@
       <c r="C101" t="s">
         <v>105</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E101" s="17" t="s">
@@ -3285,7 +3303,7 @@
       <c r="C102" t="s">
         <v>152</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E102" s="17" t="s">
@@ -3302,7 +3320,7 @@
       <c r="C103" t="s">
         <v>153</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E103" s="17" t="s">
@@ -3319,7 +3337,7 @@
       <c r="C104" t="s">
         <v>154</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E104" s="17" t="s">
@@ -3336,7 +3354,7 @@
       <c r="C105" t="s">
         <v>155</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E105" s="17" t="s">
@@ -3353,7 +3371,7 @@
       <c r="C106" t="s">
         <v>156</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="17" t="s">
         <v>151</v>
       </c>
       <c r="E106" s="17" t="s">
@@ -3370,7 +3388,7 @@
       <c r="C107" t="s">
         <v>159</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E107" s="17" t="s">
@@ -3387,7 +3405,7 @@
       <c r="C108" t="s">
         <v>160</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E108" s="17" t="s">
@@ -3404,7 +3422,7 @@
       <c r="C109" t="s">
         <v>161</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E109" s="17" t="s">
@@ -3421,7 +3439,7 @@
       <c r="C110" t="s">
         <v>163</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="17" t="s">
         <v>164</v>
       </c>
       <c r="E110" s="17" t="s">
@@ -3438,7 +3456,7 @@
       <c r="C111" t="s">
         <v>217</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="17" t="s">
         <v>218</v>
       </c>
       <c r="E111" s="17" t="s">
@@ -3455,7 +3473,7 @@
       <c r="C112" t="s">
         <v>219</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="17" t="s">
         <v>220</v>
       </c>
       <c r="E112" s="17" t="s">
@@ -3472,7 +3490,7 @@
       <c r="C113" t="s">
         <v>221</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="17" t="s">
         <v>222</v>
       </c>
       <c r="E113" s="17" t="s">
@@ -3489,7 +3507,7 @@
       <c r="C114" t="s">
         <v>223</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="17" t="s">
         <v>224</v>
       </c>
       <c r="E114" s="17" t="s">
@@ -3506,7 +3524,7 @@
       <c r="C115" t="s">
         <v>227</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E115" s="17" t="s">
@@ -3523,7 +3541,7 @@
       <c r="C116" t="s">
         <v>228</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="17" t="s">
         <v>229</v>
       </c>
       <c r="E116" s="17" t="s">
@@ -3540,7 +3558,7 @@
       <c r="C117" t="s">
         <v>230</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="17" t="s">
         <v>233</v>
       </c>
       <c r="E117" s="17" t="s">
@@ -3557,7 +3575,7 @@
       <c r="C118" t="s">
         <v>231</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="17" t="s">
         <v>233</v>
       </c>
       <c r="E118" s="17" t="s">
@@ -3574,7 +3592,7 @@
       <c r="C119" t="s">
         <v>227</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="17" t="s">
         <v>257</v>
       </c>
       <c r="E119" s="17" t="s">
@@ -3591,7 +3609,7 @@
       <c r="C120" t="s">
         <v>258</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E120" s="17" t="s">
@@ -3608,7 +3626,7 @@
       <c r="C121" t="s">
         <v>259</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E121" s="17" t="s">
@@ -3625,7 +3643,7 @@
       <c r="C122" t="s">
         <v>260</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="17" t="s">
         <v>261</v>
       </c>
       <c r="E122" s="17" t="s">
@@ -3642,7 +3660,7 @@
       <c r="C123" t="s">
         <v>262</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="17" t="s">
         <v>263</v>
       </c>
       <c r="E123" s="17" t="s">
@@ -3659,7 +3677,7 @@
       <c r="C124" t="s">
         <v>264</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E124" s="17" t="s">
@@ -3676,7 +3694,7 @@
       <c r="C125" t="s">
         <v>265</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E125" s="17" t="s">
@@ -3693,7 +3711,7 @@
       <c r="C126" t="s">
         <v>266</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="17" t="s">
         <v>269</v>
       </c>
       <c r="E126" s="17" t="s">
@@ -3710,7 +3728,7 @@
       <c r="C127" t="s">
         <v>267</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="17" t="s">
         <v>270</v>
       </c>
       <c r="E127" s="17" t="s">
@@ -3727,7 +3745,7 @@
       <c r="C128" t="s">
         <v>268</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="17" t="s">
         <v>270</v>
       </c>
       <c r="E128" s="17" t="s">
@@ -3744,7 +3762,7 @@
       <c r="C129" t="s">
         <v>271</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="17" t="s">
         <v>274</v>
       </c>
       <c r="E129" s="17" t="s">
@@ -3761,7 +3779,7 @@
       <c r="C130" t="s">
         <v>272</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="17" t="s">
         <v>274</v>
       </c>
       <c r="E130" s="17" t="s">
@@ -3778,7 +3796,7 @@
       <c r="C131" t="s">
         <v>273</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="17" t="s">
         <v>270</v>
       </c>
       <c r="E131" s="17" t="s">
@@ -3795,7 +3813,7 @@
       <c r="C132" t="s">
         <v>275</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E132" s="17" t="s">
@@ -3812,7 +3830,7 @@
       <c r="C133" t="s">
         <v>276</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E133" s="17" t="s">
@@ -3829,7 +3847,7 @@
       <c r="C134" t="s">
         <v>277</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E134" s="17" t="s">
@@ -3846,7 +3864,7 @@
       <c r="C135" t="s">
         <v>278</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E135" s="17" t="s">
@@ -3857,26 +3875,85 @@
       <c r="A136" s="8">
         <v>135</v>
       </c>
-      <c r="D136" s="2"/>
+      <c r="B136" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C136" t="s">
+        <v>280</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E136" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>136</v>
       </c>
+      <c r="B137" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C137" t="s">
+        <v>281</v>
+      </c>
+      <c r="D137" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E137" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>137</v>
       </c>
+      <c r="B138" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C138" t="s">
+        <v>282</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>138</v>
       </c>
+      <c r="B139" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C139" t="s">
+        <v>283</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>139</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C140" t="s">
+        <v>284</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E140" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863F6931-20AE-41CF-B9D8-CF428F66D1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C3CB3F-7836-4D6A-89CC-F22CBC6CE715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="292">
   <si>
     <t>London</t>
   </si>
@@ -890,6 +890,27 @@
   </si>
   <si>
     <t>The Bumble Inn</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Estaminet Hein</t>
+  </si>
+  <si>
+    <t>Célestin</t>
+  </si>
+  <si>
+    <t>L'Illustration</t>
+  </si>
+  <si>
+    <t>La Capsule Lille</t>
+  </si>
+  <si>
+    <t>Beer Square</t>
+  </si>
+  <si>
+    <t>Le Chopp'ing</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1478,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1481,7 +1502,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5910,83 +5931,155 @@
       <c r="A80" s="8">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B80" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C80" t="s">
+        <v>286</v>
+      </c>
+      <c r="D80" t="s">
+        <v>285</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B81" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C81" t="s">
+        <v>287</v>
+      </c>
+      <c r="D81" t="s">
+        <v>285</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B82" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C82" t="s">
+        <v>288</v>
+      </c>
+      <c r="D82" t="s">
+        <v>285</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B83" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C83" t="s">
+        <v>291</v>
+      </c>
+      <c r="D83" t="s">
+        <v>285</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B84" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C84" t="s">
+        <v>289</v>
+      </c>
+      <c r="D84" t="s">
+        <v>285</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B85" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C85" t="s">
+        <v>290</v>
+      </c>
+      <c r="D85" t="s">
+        <v>285</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>95</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C3CB3F-7836-4D6A-89CC-F22CBC6CE715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD25792-B9F4-4214-B839-B83118FA3DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="301">
   <si>
     <t>London</t>
   </si>
@@ -911,6 +911,33 @@
   </si>
   <si>
     <t>Le Chopp'ing</t>
+  </si>
+  <si>
+    <t>Arras</t>
+  </si>
+  <si>
+    <t>Microbrasserie L'ARRAS'IN</t>
+  </si>
+  <si>
+    <t>BatBar Arras</t>
+  </si>
+  <si>
+    <t>Couleur Café</t>
+  </si>
+  <si>
+    <t>The French House Arras</t>
+  </si>
+  <si>
+    <t>Le Palerme</t>
+  </si>
+  <si>
+    <t>La Capsule Arras</t>
+  </si>
+  <si>
+    <t>La Brasserie du Lion</t>
+  </si>
+  <si>
+    <t>L’Élysée</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1505,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1502,7 +1529,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6033,40 +6060,136 @@
       <c r="A86" s="8">
         <v>85</v>
       </c>
+      <c r="B86" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C86" t="s">
+        <v>293</v>
+      </c>
+      <c r="D86" t="s">
+        <v>292</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>86</v>
       </c>
+      <c r="B87" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C87" t="s">
+        <v>294</v>
+      </c>
+      <c r="D87" t="s">
+        <v>292</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>87</v>
       </c>
+      <c r="B88" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C88" t="s">
+        <v>295</v>
+      </c>
+      <c r="D88" t="s">
+        <v>292</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>88</v>
       </c>
+      <c r="B89" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C89" t="s">
+        <v>296</v>
+      </c>
+      <c r="D89" t="s">
+        <v>292</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>89</v>
       </c>
+      <c r="B90" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C90" t="s">
+        <v>297</v>
+      </c>
+      <c r="D90" t="s">
+        <v>292</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>90</v>
       </c>
+      <c r="B91" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C91" t="s">
+        <v>298</v>
+      </c>
+      <c r="D91" t="s">
+        <v>292</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>91</v>
       </c>
+      <c r="B92" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C92" t="s">
+        <v>299</v>
+      </c>
+      <c r="D92" t="s">
+        <v>292</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>92</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C93" t="s">
+        <v>300</v>
+      </c>
+      <c r="D93" t="s">
+        <v>292</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD25792-B9F4-4214-B839-B83118FA3DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADC5040-DC7F-488B-B745-FA1F74FBBF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="306">
   <si>
     <t>London</t>
   </si>
@@ -938,6 +938,21 @@
   </si>
   <si>
     <t>L’Élysée</t>
+  </si>
+  <si>
+    <t>Brasserie l'Eurostar</t>
+  </si>
+  <si>
+    <t>La Civette de Lens</t>
+  </si>
+  <si>
+    <t>L’ImBeertinence</t>
+  </si>
+  <si>
+    <t>Volfoni</t>
+  </si>
+  <si>
+    <t>Lens</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1520,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1529,7 +1544,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6196,93 +6211,141 @@
       <c r="A94" s="8">
         <v>93</v>
       </c>
+      <c r="B94" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C94" t="s">
+        <v>301</v>
+      </c>
+      <c r="D94" t="s">
+        <v>292</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>94</v>
       </c>
+      <c r="B95" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C95" t="s">
+        <v>303</v>
+      </c>
+      <c r="D95" t="s">
+        <v>305</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B96" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C96" t="s">
+        <v>302</v>
+      </c>
+      <c r="D96" t="s">
+        <v>305</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B97" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C97" t="s">
+        <v>304</v>
+      </c>
+      <c r="D97" t="s">
+        <v>292</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>111</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADC5040-DC7F-488B-B745-FA1F74FBBF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F9DE1-23E2-4020-A722-426FF6F92772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="307">
   <si>
     <t>London</t>
   </si>
@@ -943,9 +943,6 @@
     <t>Brasserie l'Eurostar</t>
   </si>
   <si>
-    <t>La Civette de Lens</t>
-  </si>
-  <si>
     <t>L’ImBeertinence</t>
   </si>
   <si>
@@ -953,6 +950,12 @@
   </si>
   <si>
     <t>Lens</t>
+  </si>
+  <si>
+    <t>Mercure Hotel</t>
+  </si>
+  <si>
+    <t>La Civette</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1523,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6232,10 +6235,10 @@
         <v>46242</v>
       </c>
       <c r="C95" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D95" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>166</v>
@@ -6249,10 +6252,10 @@
         <v>46242</v>
       </c>
       <c r="C96" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D96" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>166</v>
@@ -6266,7 +6269,7 @@
         <v>46242</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D97" t="s">
         <v>292</v>
@@ -6278,6 +6281,18 @@
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>97</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C98" t="s">
+        <v>303</v>
+      </c>
+      <c r="D98" t="s">
+        <v>292</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F9DE1-23E2-4020-A722-426FF6F92772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CEA3A7-E617-4BD9-A8B2-DD06CDD0218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="317">
   <si>
     <t>London</t>
   </si>
@@ -956,6 +956,36 @@
   </si>
   <si>
     <t>La Civette</t>
+  </si>
+  <si>
+    <t>Moeder Lambic Fontainas</t>
+  </si>
+  <si>
+    <t>Beer Capital</t>
+  </si>
+  <si>
+    <t>GourmetBar</t>
+  </si>
+  <si>
+    <t>A l’Imaige Nostre-Dame</t>
+  </si>
+  <si>
+    <t>Toone</t>
+  </si>
+  <si>
+    <t>Poechenellekelder</t>
+  </si>
+  <si>
+    <t>Little Delirium</t>
+  </si>
+  <si>
+    <t>Au Brasseur</t>
+  </si>
+  <si>
+    <t>Brussels</t>
+  </si>
+  <si>
+    <t>be</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1553,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1547,7 +1577,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6299,40 +6329,136 @@
       <c r="A99" s="8">
         <v>98</v>
       </c>
+      <c r="B99" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C99" t="s">
+        <v>307</v>
+      </c>
+      <c r="D99" t="s">
+        <v>315</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>99</v>
       </c>
+      <c r="B100" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C100" t="s">
+        <v>308</v>
+      </c>
+      <c r="D100" t="s">
+        <v>315</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>100</v>
       </c>
+      <c r="B101" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C101" t="s">
+        <v>309</v>
+      </c>
+      <c r="D101" t="s">
+        <v>315</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>101</v>
       </c>
+      <c r="B102" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C102" t="s">
+        <v>310</v>
+      </c>
+      <c r="D102" t="s">
+        <v>315</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>102</v>
       </c>
+      <c r="B103" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C103" t="s">
+        <v>311</v>
+      </c>
+      <c r="D103" t="s">
+        <v>315</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>103</v>
       </c>
+      <c r="B104" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C104" t="s">
+        <v>312</v>
+      </c>
+      <c r="D104" t="s">
+        <v>315</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>104</v>
       </c>
+      <c r="B105" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C105" t="s">
+        <v>313</v>
+      </c>
+      <c r="D105" t="s">
+        <v>315</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>105</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C106" t="s">
+        <v>314</v>
+      </c>
+      <c r="D106" t="s">
+        <v>315</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CEA3A7-E617-4BD9-A8B2-DD06CDD0218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CEA3A7-E617-4BD9-A8B2-DD06CDD0218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350579DA-85F0-4D93-908C-F29971C5E7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="321">
   <si>
     <t>London</t>
   </si>
@@ -986,6 +986,18 @@
   </si>
   <si>
     <t>be</t>
+  </si>
+  <si>
+    <t>The Old House at Home</t>
+  </si>
+  <si>
+    <t>Overton</t>
+  </si>
+  <si>
+    <t>The Watership Down</t>
+  </si>
+  <si>
+    <t>Freefolk</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1541,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1577,7 +1589,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4056,10 +4068,34 @@
       <c r="A141" s="8">
         <v>140</v>
       </c>
+      <c r="B141" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C141" t="s">
+        <v>317</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E141" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>141</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C142" t="s">
+        <v>319</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="E142" s="17" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350579DA-85F0-4D93-908C-F29971C5E7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68D41F2-84E0-41A0-BD52-31E85BF98125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="325">
   <si>
     <t>London</t>
   </si>
@@ -998,6 +998,18 @@
   </si>
   <si>
     <t>Freefolk</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>The Moon in the Square</t>
+  </si>
+  <si>
+    <t>The Mary Shelley</t>
+  </si>
+  <si>
+    <t>The Goat and Tricycle</t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1553,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1589,7 +1601,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1651,7 +1663,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4102,88 +4114,136 @@
       <c r="A143" s="8">
         <v>142</v>
       </c>
+      <c r="B143" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C143" t="s">
+        <v>157</v>
+      </c>
+      <c r="D143" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E143" s="17" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>143</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B144" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C144" t="s">
+        <v>323</v>
+      </c>
+      <c r="D144" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E144" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C145" t="s">
+        <v>322</v>
+      </c>
+      <c r="D145" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E145" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B146" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C146" t="s">
+        <v>324</v>
+      </c>
+      <c r="D146" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E146" s="17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>159</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68D41F2-84E0-41A0-BD52-31E85BF98125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44428578-4082-4024-9106-504C55683447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="327">
   <si>
     <t>London</t>
   </si>
@@ -805,9 +805,6 @@
     <t>The Harbour</t>
   </si>
   <si>
-    <t>gb</t>
-  </si>
-  <si>
     <t>Sherborne St John</t>
   </si>
   <si>
@@ -1010,6 +1007,15 @@
   </si>
   <si>
     <t>The Goat and Tricycle</t>
+  </si>
+  <si>
+    <t>Little London</t>
+  </si>
+  <si>
+    <t>gb-eng</t>
+  </si>
+  <si>
+    <t>gb-wls</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="G2"/>
     </row>
@@ -1546,14 +1552,14 @@
         <v>10</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1601,7 +1607,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1618,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12"/>
@@ -1637,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12"/>
@@ -1680,7 +1686,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="15"/>
@@ -1733,7 +1739,7 @@
         <v>46</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1767,7 +1773,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1784,7 +1790,7 @@
         <v>49</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1801,7 +1807,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16"/>
@@ -1820,7 +1826,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17"/>
@@ -1839,7 +1845,7 @@
         <v>53</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18"/>
@@ -1858,7 +1864,7 @@
         <v>53</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19"/>
@@ -1877,7 +1883,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20"/>
@@ -1896,7 +1902,7 @@
         <v>53</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21"/>
@@ -1915,7 +1921,7 @@
         <v>53</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22"/>
@@ -1934,7 +1940,7 @@
         <v>53</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23"/>
@@ -1972,7 +1978,7 @@
         <v>62</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25"/>
@@ -1991,7 +1997,7 @@
         <v>62</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26"/>
@@ -2010,7 +2016,7 @@
         <v>62</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27"/>
@@ -2029,7 +2035,7 @@
         <v>62</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28"/>
@@ -2048,7 +2054,7 @@
         <v>62</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29"/>
@@ -2067,7 +2073,7 @@
         <v>53</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30"/>
@@ -2086,7 +2092,7 @@
         <v>53</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31"/>
@@ -2105,7 +2111,7 @@
         <v>53</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32"/>
@@ -2124,7 +2130,7 @@
         <v>53</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33"/>
@@ -2143,7 +2149,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34"/>
@@ -2162,7 +2168,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35"/>
@@ -2181,7 +2187,7 @@
         <v>74</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36"/>
@@ -2200,7 +2206,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37"/>
@@ -2219,7 +2225,7 @@
         <v>76</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38"/>
@@ -2238,7 +2244,7 @@
         <v>76</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39"/>
@@ -2257,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40"/>
@@ -2276,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41"/>
@@ -2295,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42"/>
@@ -2314,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43"/>
@@ -2352,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45"/>
@@ -2371,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46"/>
@@ -2390,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47"/>
@@ -2409,7 +2415,7 @@
         <v>88</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48"/>
@@ -2428,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49"/>
@@ -2485,7 +2491,7 @@
         <v>93</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52"/>
@@ -2504,7 +2510,7 @@
         <v>93</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53"/>
@@ -2523,7 +2529,7 @@
         <v>93</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54"/>
@@ -2542,7 +2548,7 @@
         <v>93</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55"/>
@@ -2561,7 +2567,7 @@
         <v>93</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56"/>
@@ -2580,7 +2586,7 @@
         <v>93</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57"/>
@@ -2618,7 +2624,7 @@
         <v>93</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59"/>
@@ -2637,7 +2643,7 @@
         <v>93</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60"/>
@@ -2656,7 +2662,7 @@
         <v>93</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61"/>
@@ -2675,7 +2681,7 @@
         <v>93</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62"/>
@@ -2694,7 +2700,7 @@
         <v>93</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63"/>
@@ -2713,7 +2719,7 @@
         <v>93</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64"/>
@@ -2732,7 +2738,7 @@
         <v>108</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65"/>
@@ -2751,7 +2757,7 @@
         <v>108</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66"/>
@@ -2789,7 +2795,7 @@
         <v>111</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68"/>
@@ -2808,7 +2814,7 @@
         <v>111</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69"/>
@@ -2827,7 +2833,7 @@
         <v>111</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70"/>
@@ -2846,7 +2852,7 @@
         <v>111</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71"/>
@@ -2865,7 +2871,7 @@
         <v>111</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72"/>
@@ -2884,7 +2890,7 @@
         <v>111</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73"/>
@@ -2903,7 +2909,7 @@
         <v>111</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74"/>
@@ -2922,7 +2928,7 @@
         <v>111</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75"/>
@@ -2941,7 +2947,7 @@
         <v>111</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76"/>
@@ -2960,7 +2966,7 @@
         <v>111</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77"/>
@@ -2998,7 +3004,7 @@
         <v>111</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79"/>
@@ -3017,7 +3023,7 @@
         <v>111</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80"/>
@@ -3036,7 +3042,7 @@
         <v>111</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81"/>
@@ -3074,7 +3080,7 @@
         <v>111</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83"/>
@@ -3093,7 +3099,7 @@
         <v>111</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84"/>
@@ -3112,7 +3118,7 @@
         <v>130</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85"/>
@@ -3131,7 +3137,7 @@
         <v>130</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86"/>
@@ -3150,7 +3156,7 @@
         <v>140</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87"/>
@@ -3169,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88"/>
@@ -3188,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89"/>
@@ -3207,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90"/>
@@ -3226,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91"/>
@@ -3245,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92"/>
@@ -3283,7 +3289,7 @@
         <v>151</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94"/>
@@ -3302,7 +3308,7 @@
         <v>151</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95"/>
@@ -3321,7 +3327,7 @@
         <v>151</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96"/>
@@ -3340,7 +3346,7 @@
         <v>151</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97"/>
@@ -3359,7 +3365,7 @@
         <v>151</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3376,7 +3382,7 @@
         <v>151</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3393,7 +3399,7 @@
         <v>151</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3410,7 +3416,7 @@
         <v>151</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -3427,7 +3433,7 @@
         <v>151</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -3444,7 +3450,7 @@
         <v>151</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -3461,7 +3467,7 @@
         <v>151</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -3495,7 +3501,7 @@
         <v>151</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -3512,7 +3518,7 @@
         <v>162</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -3529,7 +3535,7 @@
         <v>162</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -3580,7 +3586,7 @@
         <v>218</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -3597,7 +3603,7 @@
         <v>220</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3614,7 +3620,7 @@
         <v>222</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3631,7 +3637,7 @@
         <v>224</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3648,7 +3654,7 @@
         <v>162</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3665,7 +3671,7 @@
         <v>229</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3682,7 +3688,7 @@
         <v>233</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3713,10 +3719,10 @@
         <v>227</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3727,13 +3733,13 @@
         <v>46214</v>
       </c>
       <c r="C120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D120" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3744,13 +3750,13 @@
         <v>46214</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D121" s="17" t="s">
         <v>88</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3761,13 +3767,13 @@
         <v>46218</v>
       </c>
       <c r="C122" t="s">
+        <v>259</v>
+      </c>
+      <c r="D122" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D122" s="17" t="s">
-        <v>261</v>
-      </c>
       <c r="E122" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3778,13 +3784,13 @@
         <v>46218</v>
       </c>
       <c r="C123" t="s">
+        <v>261</v>
+      </c>
+      <c r="D123" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="D123" s="17" t="s">
-        <v>263</v>
-      </c>
       <c r="E123" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3795,13 +3801,13 @@
         <v>46220</v>
       </c>
       <c r="C124" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D124" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3812,13 +3818,13 @@
         <v>46220</v>
       </c>
       <c r="C125" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D125" s="17" t="s">
         <v>162</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3829,13 +3835,13 @@
         <v>46224</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3846,13 +3852,13 @@
         <v>46224</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3863,13 +3869,13 @@
         <v>46224</v>
       </c>
       <c r="C128" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3880,13 +3886,13 @@
         <v>46225</v>
       </c>
       <c r="C129" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3897,13 +3903,13 @@
         <v>46225</v>
       </c>
       <c r="C130" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3914,13 +3920,13 @@
         <v>46225</v>
       </c>
       <c r="C131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3931,13 +3937,13 @@
         <v>46226</v>
       </c>
       <c r="C132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D132" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3948,13 +3954,13 @@
         <v>46227</v>
       </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D133" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3965,13 +3971,13 @@
         <v>46227</v>
       </c>
       <c r="C134" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D134" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3982,13 +3988,13 @@
         <v>46227</v>
       </c>
       <c r="C135" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D135" s="17" t="s">
         <v>93</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3999,13 +4005,13 @@
         <v>46228</v>
       </c>
       <c r="C136" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -4016,13 +4022,13 @@
         <v>46228</v>
       </c>
       <c r="C137" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -4033,10 +4039,10 @@
         <v>46228</v>
       </c>
       <c r="C138" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E138" s="17" t="s">
         <v>132</v>
@@ -4050,13 +4056,13 @@
         <v>46228</v>
       </c>
       <c r="C139" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -4067,13 +4073,13 @@
         <v>46228</v>
       </c>
       <c r="C140" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -4084,13 +4090,13 @@
         <v>46249</v>
       </c>
       <c r="C141" t="s">
+        <v>316</v>
+      </c>
+      <c r="D141" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="D141" s="17" t="s">
-        <v>318</v>
-      </c>
       <c r="E141" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4101,13 +4107,13 @@
         <v>46249</v>
       </c>
       <c r="C142" t="s">
+        <v>318</v>
+      </c>
+      <c r="D142" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="D142" s="17" t="s">
-        <v>320</v>
-      </c>
       <c r="E142" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4121,10 +4127,10 @@
         <v>157</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4135,10 +4141,10 @@
         <v>46254</v>
       </c>
       <c r="C144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E144" s="17" t="s">
         <v>132</v>
@@ -4152,10 +4158,10 @@
         <v>46254</v>
       </c>
       <c r="C145" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E145" s="17" t="s">
         <v>132</v>
@@ -4169,18 +4175,30 @@
         <v>46254</v>
       </c>
       <c r="C146" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>146</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46255</v>
+      </c>
+      <c r="C147" t="s">
+        <v>152</v>
+      </c>
+      <c r="D147" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="E147" s="17" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -6106,10 +6124,10 @@
         <v>46240</v>
       </c>
       <c r="C80" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>166</v>
@@ -6123,10 +6141,10 @@
         <v>46240</v>
       </c>
       <c r="C81" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D81" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>166</v>
@@ -6140,10 +6158,10 @@
         <v>46240</v>
       </c>
       <c r="C82" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D82" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>166</v>
@@ -6157,10 +6175,10 @@
         <v>46240</v>
       </c>
       <c r="C83" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>166</v>
@@ -6174,10 +6192,10 @@
         <v>46240</v>
       </c>
       <c r="C84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D84" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>166</v>
@@ -6191,10 +6209,10 @@
         <v>46240</v>
       </c>
       <c r="C85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D85" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
@@ -6208,10 +6226,10 @@
         <v>46241</v>
       </c>
       <c r="C86" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D86" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>166</v>
@@ -6225,10 +6243,10 @@
         <v>46241</v>
       </c>
       <c r="C87" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>166</v>
@@ -6242,10 +6260,10 @@
         <v>46241</v>
       </c>
       <c r="C88" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D88" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>166</v>
@@ -6259,10 +6277,10 @@
         <v>46241</v>
       </c>
       <c r="C89" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>166</v>
@@ -6276,10 +6294,10 @@
         <v>46241</v>
       </c>
       <c r="C90" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>166</v>
@@ -6293,10 +6311,10 @@
         <v>46241</v>
       </c>
       <c r="C91" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D91" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>166</v>
@@ -6310,10 +6328,10 @@
         <v>46241</v>
       </c>
       <c r="C92" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D92" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>166</v>
@@ -6327,10 +6345,10 @@
         <v>46241</v>
       </c>
       <c r="C93" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D93" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>166</v>
@@ -6344,10 +6362,10 @@
         <v>46242</v>
       </c>
       <c r="C94" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D94" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>166</v>
@@ -6361,10 +6379,10 @@
         <v>46242</v>
       </c>
       <c r="C95" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D95" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>166</v>
@@ -6378,10 +6396,10 @@
         <v>46242</v>
       </c>
       <c r="C96" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D96" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>166</v>
@@ -6395,10 +6413,10 @@
         <v>46242</v>
       </c>
       <c r="C97" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>166</v>
@@ -6412,10 +6430,10 @@
         <v>46242</v>
       </c>
       <c r="C98" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D98" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>166</v>
@@ -6429,13 +6447,13 @@
         <v>46243</v>
       </c>
       <c r="C99" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D99" t="s">
+        <v>314</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -6446,13 +6464,13 @@
         <v>46243</v>
       </c>
       <c r="C100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D100" t="s">
+        <v>314</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -6463,13 +6481,13 @@
         <v>46243</v>
       </c>
       <c r="C101" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D101" t="s">
+        <v>314</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -6480,13 +6498,13 @@
         <v>46243</v>
       </c>
       <c r="C102" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D102" t="s">
+        <v>314</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -6497,13 +6515,13 @@
         <v>46243</v>
       </c>
       <c r="C103" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D103" t="s">
+        <v>314</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -6514,13 +6532,13 @@
         <v>46243</v>
       </c>
       <c r="C104" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D104" t="s">
+        <v>314</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -6531,13 +6549,13 @@
         <v>46243</v>
       </c>
       <c r="C105" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s">
+        <v>314</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -6548,13 +6566,13 @@
         <v>46243</v>
       </c>
       <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
         <v>314</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44428578-4082-4024-9106-504C55683447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CF868A-3615-42E0-BFD9-910C289CB377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
   <si>
     <t>London</t>
   </si>
@@ -961,9 +961,6 @@
     <t>Beer Capital</t>
   </si>
   <si>
-    <t>GourmetBar</t>
-  </si>
-  <si>
     <t>A l’Imaige Nostre-Dame</t>
   </si>
   <si>
@@ -1016,6 +1013,12 @@
   </si>
   <si>
     <t>gb-wls</t>
+  </si>
+  <si>
+    <t>The Bowls Club</t>
+  </si>
+  <si>
+    <t>GourmetBar (Novotel)</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G2"/>
     </row>
@@ -1552,14 +1555,14 @@
         <v>10</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1607,7 +1610,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1624,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12"/>
@@ -1643,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12"/>
@@ -1686,7 +1689,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="15"/>
@@ -1739,7 +1742,7 @@
         <v>46</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1773,7 +1776,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1790,7 +1793,7 @@
         <v>49</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1807,7 +1810,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16"/>
@@ -1826,7 +1829,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17"/>
@@ -1845,7 +1848,7 @@
         <v>53</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18"/>
@@ -1864,7 +1867,7 @@
         <v>53</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19"/>
@@ -1883,7 +1886,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20"/>
@@ -1902,7 +1905,7 @@
         <v>53</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21"/>
@@ -1921,7 +1924,7 @@
         <v>53</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22"/>
@@ -1940,7 +1943,7 @@
         <v>53</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23"/>
@@ -1978,7 +1981,7 @@
         <v>62</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25"/>
@@ -1997,7 +2000,7 @@
         <v>62</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26"/>
@@ -2016,7 +2019,7 @@
         <v>62</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27"/>
@@ -2035,7 +2038,7 @@
         <v>62</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28"/>
@@ -2054,7 +2057,7 @@
         <v>62</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29"/>
@@ -2073,7 +2076,7 @@
         <v>53</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30"/>
@@ -2092,7 +2095,7 @@
         <v>53</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31"/>
@@ -2111,7 +2114,7 @@
         <v>53</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32"/>
@@ -2130,7 +2133,7 @@
         <v>53</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33"/>
@@ -2149,7 +2152,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34"/>
@@ -2168,7 +2171,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35"/>
@@ -2187,7 +2190,7 @@
         <v>74</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36"/>
@@ -2206,7 +2209,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37"/>
@@ -2225,7 +2228,7 @@
         <v>76</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38"/>
@@ -2244,7 +2247,7 @@
         <v>76</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39"/>
@@ -2263,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40"/>
@@ -2282,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41"/>
@@ -2301,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42"/>
@@ -2320,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43"/>
@@ -2358,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45"/>
@@ -2377,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46"/>
@@ -2396,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47"/>
@@ -2415,7 +2418,7 @@
         <v>88</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48"/>
@@ -2434,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49"/>
@@ -2491,7 +2494,7 @@
         <v>93</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52"/>
@@ -2510,7 +2513,7 @@
         <v>93</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53"/>
@@ -2529,7 +2532,7 @@
         <v>93</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54"/>
@@ -2548,7 +2551,7 @@
         <v>93</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55"/>
@@ -2567,7 +2570,7 @@
         <v>93</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56"/>
@@ -2586,7 +2589,7 @@
         <v>93</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57"/>
@@ -2624,7 +2627,7 @@
         <v>93</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59"/>
@@ -2643,7 +2646,7 @@
         <v>93</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60"/>
@@ -2662,7 +2665,7 @@
         <v>93</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61"/>
@@ -2681,7 +2684,7 @@
         <v>93</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62"/>
@@ -2700,7 +2703,7 @@
         <v>93</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63"/>
@@ -2719,7 +2722,7 @@
         <v>93</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64"/>
@@ -2738,7 +2741,7 @@
         <v>108</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65"/>
@@ -2757,7 +2760,7 @@
         <v>108</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66"/>
@@ -2795,7 +2798,7 @@
         <v>111</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68"/>
@@ -2814,7 +2817,7 @@
         <v>111</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69"/>
@@ -2833,7 +2836,7 @@
         <v>111</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70"/>
@@ -2852,7 +2855,7 @@
         <v>111</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71"/>
@@ -2871,7 +2874,7 @@
         <v>111</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72"/>
@@ -2890,7 +2893,7 @@
         <v>111</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73"/>
@@ -2909,7 +2912,7 @@
         <v>111</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74"/>
@@ -2928,7 +2931,7 @@
         <v>111</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75"/>
@@ -2947,7 +2950,7 @@
         <v>111</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76"/>
@@ -2966,7 +2969,7 @@
         <v>111</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77"/>
@@ -3004,7 +3007,7 @@
         <v>111</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79"/>
@@ -3023,7 +3026,7 @@
         <v>111</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80"/>
@@ -3042,7 +3045,7 @@
         <v>111</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81"/>
@@ -3080,7 +3083,7 @@
         <v>111</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83"/>
@@ -3099,7 +3102,7 @@
         <v>111</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84"/>
@@ -3118,7 +3121,7 @@
         <v>130</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85"/>
@@ -3137,7 +3140,7 @@
         <v>130</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86"/>
@@ -3156,7 +3159,7 @@
         <v>140</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87"/>
@@ -3175,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88"/>
@@ -3194,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89"/>
@@ -3213,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90"/>
@@ -3232,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91"/>
@@ -3251,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92"/>
@@ -3289,7 +3292,7 @@
         <v>151</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94"/>
@@ -3308,7 +3311,7 @@
         <v>151</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95"/>
@@ -3327,7 +3330,7 @@
         <v>151</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96"/>
@@ -3346,7 +3349,7 @@
         <v>151</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97"/>
@@ -3365,7 +3368,7 @@
         <v>151</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3382,7 +3385,7 @@
         <v>151</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3399,7 +3402,7 @@
         <v>151</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3416,7 +3419,7 @@
         <v>151</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -3433,7 +3436,7 @@
         <v>151</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -3450,7 +3453,7 @@
         <v>151</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -3467,7 +3470,7 @@
         <v>151</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -3501,7 +3504,7 @@
         <v>151</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -3518,7 +3521,7 @@
         <v>162</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -3535,7 +3538,7 @@
         <v>162</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -3586,7 +3589,7 @@
         <v>218</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -3603,7 +3606,7 @@
         <v>220</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3620,7 +3623,7 @@
         <v>222</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3637,7 +3640,7 @@
         <v>224</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3654,7 +3657,7 @@
         <v>162</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3671,7 +3674,7 @@
         <v>229</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3688,7 +3691,7 @@
         <v>233</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3722,7 +3725,7 @@
         <v>256</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3739,7 +3742,7 @@
         <v>88</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3756,7 +3759,7 @@
         <v>88</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3773,7 +3776,7 @@
         <v>260</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3790,7 +3793,7 @@
         <v>262</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3807,7 +3810,7 @@
         <v>162</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3824,7 +3827,7 @@
         <v>162</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3841,7 +3844,7 @@
         <v>268</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3858,7 +3861,7 @@
         <v>269</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3875,7 +3878,7 @@
         <v>269</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3892,7 +3895,7 @@
         <v>273</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3909,7 +3912,7 @@
         <v>273</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3926,7 +3929,7 @@
         <v>269</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3943,7 +3946,7 @@
         <v>93</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3960,7 +3963,7 @@
         <v>93</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3977,7 +3980,7 @@
         <v>93</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3994,7 +3997,7 @@
         <v>93</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -4011,7 +4014,7 @@
         <v>278</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -4028,7 +4031,7 @@
         <v>278</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -4062,7 +4065,7 @@
         <v>278</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -4079,7 +4082,7 @@
         <v>278</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -4090,13 +4093,13 @@
         <v>46249</v>
       </c>
       <c r="C141" t="s">
+        <v>315</v>
+      </c>
+      <c r="D141" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="D141" s="17" t="s">
-        <v>317</v>
-      </c>
       <c r="E141" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4107,13 +4110,13 @@
         <v>46249</v>
       </c>
       <c r="C142" t="s">
+        <v>317</v>
+      </c>
+      <c r="D142" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="D142" s="17" t="s">
-        <v>319</v>
-      </c>
       <c r="E142" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4127,10 +4130,10 @@
         <v>157</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4141,10 +4144,10 @@
         <v>46254</v>
       </c>
       <c r="C144" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E144" s="17" t="s">
         <v>132</v>
@@ -4158,10 +4161,10 @@
         <v>46254</v>
       </c>
       <c r="C145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E145" s="17" t="s">
         <v>132</v>
@@ -4175,13 +4178,13 @@
         <v>46254</v>
       </c>
       <c r="C146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -4195,15 +4198,27 @@
         <v>152</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>147</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C148" t="s">
+        <v>326</v>
+      </c>
+      <c r="D148" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -6450,10 +6465,10 @@
         <v>306</v>
       </c>
       <c r="D99" t="s">
+        <v>313</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -6467,10 +6482,10 @@
         <v>307</v>
       </c>
       <c r="D100" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -6481,13 +6496,13 @@
         <v>46243</v>
       </c>
       <c r="C101" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="D101" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -6498,13 +6513,13 @@
         <v>46243</v>
       </c>
       <c r="C102" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D102" t="s">
+        <v>313</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -6515,13 +6530,13 @@
         <v>46243</v>
       </c>
       <c r="C103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D103" t="s">
+        <v>313</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -6532,13 +6547,13 @@
         <v>46243</v>
       </c>
       <c r="C104" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D104" t="s">
+        <v>313</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -6549,13 +6564,13 @@
         <v>46243</v>
       </c>
       <c r="C105" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D105" t="s">
+        <v>313</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -6566,13 +6581,13 @@
         <v>46243</v>
       </c>
       <c r="C106" t="s">
+        <v>312</v>
+      </c>
+      <c r="D106" t="s">
         <v>313</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CF868A-3615-42E0-BFD9-910C289CB377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7708520A-7A1F-496F-BBF1-D112A855339E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="329">
   <si>
     <t>London</t>
   </si>
@@ -1019,6 +1019,9 @@
   </si>
   <si>
     <t>GourmetBar (Novotel)</t>
+  </si>
+  <si>
+    <t>The Jibbers Arms</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1610,7 +1613,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4224,6 +4227,18 @@
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>148</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C149" t="s">
+        <v>328</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7708520A-7A1F-496F-BBF1-D112A855339E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908B75DA-D50B-4799-A679-B451BBE5E863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="329">
   <si>
     <t>London</t>
   </si>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4245,10 +4245,34 @@
       <c r="A150" s="8">
         <v>149</v>
       </c>
+      <c r="B150" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C150" t="s">
+        <v>328</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C151" t="s">
+        <v>328</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908B75DA-D50B-4799-A679-B451BBE5E863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2921CF-205D-41B3-89E9-7ED787446D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
   <si>
     <t>London</t>
   </si>
@@ -1019,9 +1019,6 @@
   </si>
   <si>
     <t>GourmetBar (Novotel)</t>
-  </si>
-  <si>
-    <t>The Jibbers Arms</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1562,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,7 +1610,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4228,51 +4225,15 @@
       <c r="A149" s="8">
         <v>148</v>
       </c>
-      <c r="B149" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C149" t="s">
-        <v>328</v>
-      </c>
-      <c r="D149" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E149" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
-      <c r="B150" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C150" t="s">
-        <v>328</v>
-      </c>
-      <c r="D150" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E150" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
-      </c>
-      <c r="B151" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C151" t="s">
-        <v>328</v>
-      </c>
-      <c r="D151" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E151" s="17" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2921CF-205D-41B3-89E9-7ED787446D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5966299-3B8A-4BC8-87EA-CF833052A8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="329">
   <si>
     <t>London</t>
   </si>
@@ -1019,6 +1019,9 @@
   </si>
   <si>
     <t>GourmetBar (Novotel)</t>
+  </si>
+  <si>
+    <t>The Jibbers Arms</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1610,7 +1613,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4225,15 +4228,51 @@
       <c r="A149" s="8">
         <v>148</v>
       </c>
+      <c r="B149" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C149" t="s">
+        <v>328</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
+      <c r="B150" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C150" t="s">
+        <v>328</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C151" t="s">
+        <v>328</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5966299-3B8A-4BC8-87EA-CF833052A8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FC502B-AE60-4F8B-8A49-796E93B5827F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="329">
   <si>
     <t>London</t>
   </si>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4279,15 +4279,51 @@
       <c r="A152" s="8">
         <v>151</v>
       </c>
+      <c r="B152" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C152" t="s">
+        <v>328</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
+      <c r="B153" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C153" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C154" t="s">
+        <v>328</v>
+      </c>
+      <c r="D154" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E154" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FC502B-AE60-4F8B-8A49-796E93B5827F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38497D32-ED7F-44DE-A01E-3B5378677110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="329">
   <si>
     <t>London</t>
   </si>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4330,15 +4330,51 @@
       <c r="A155" s="8">
         <v>154</v>
       </c>
+      <c r="B155" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C155" t="s">
+        <v>328</v>
+      </c>
+      <c r="D155" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E155" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
       </c>
+      <c r="B156" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C156" t="s">
+        <v>328</v>
+      </c>
+      <c r="D156" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E156" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C157" t="s">
+        <v>328</v>
+      </c>
+      <c r="D157" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E157" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38497D32-ED7F-44DE-A01E-3B5378677110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FA4E6B-FA5C-44FC-A2B6-FB9CE0DF41F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="21132" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
   <si>
     <t>London</t>
   </si>
@@ -1019,9 +1019,6 @@
   </si>
   <si>
     <t>GourmetBar (Novotel)</t>
-  </si>
-  <si>
-    <t>The Jibbers Arms</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1562,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,7 +1610,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4228,153 +4225,45 @@
       <c r="A149" s="8">
         <v>148</v>
       </c>
-      <c r="B149" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C149" t="s">
-        <v>328</v>
-      </c>
-      <c r="D149" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E149" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
-      <c r="B150" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C150" t="s">
-        <v>328</v>
-      </c>
-      <c r="D150" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E150" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
       </c>
-      <c r="B151" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C151" t="s">
-        <v>328</v>
-      </c>
-      <c r="D151" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E151" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>151</v>
       </c>
-      <c r="B152" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C152" t="s">
-        <v>328</v>
-      </c>
-      <c r="D152" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E152" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
-      <c r="B153" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C153" t="s">
-        <v>328</v>
-      </c>
-      <c r="D153" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E153" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
       </c>
-      <c r="B154" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C154" t="s">
-        <v>328</v>
-      </c>
-      <c r="D154" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E154" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>154</v>
       </c>
-      <c r="B155" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C155" t="s">
-        <v>328</v>
-      </c>
-      <c r="D155" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E155" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
       </c>
-      <c r="B156" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C156" t="s">
-        <v>328</v>
-      </c>
-      <c r="D156" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E156" s="17" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
-      </c>
-      <c r="B157" s="1">
-        <v>46256</v>
-      </c>
-      <c r="C157" t="s">
-        <v>328</v>
-      </c>
-      <c r="D157" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E157" s="17" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FA4E6B-FA5C-44FC-A2B6-FB9CE0DF41F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B713A5A5-F814-466E-9352-F02769BE4988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="21132" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="337">
   <si>
     <t>London</t>
   </si>
@@ -1019,6 +1019,33 @@
   </si>
   <si>
     <t>GourmetBar (Novotel)</t>
+  </si>
+  <si>
+    <t>Derby</t>
+  </si>
+  <si>
+    <t>The Brasshouse</t>
+  </si>
+  <si>
+    <t>The Soloman Cutler</t>
+  </si>
+  <si>
+    <t>The Brunswick Inn</t>
+  </si>
+  <si>
+    <t>The Alexandra Hotel</t>
+  </si>
+  <si>
+    <t>The Royal Standard</t>
+  </si>
+  <si>
+    <t>The Standing Order</t>
+  </si>
+  <si>
+    <t>The Victoria Inn</t>
+  </si>
+  <si>
+    <t>The Colmore</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1589,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1610,7 +1637,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1672,7 +1699,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4225,40 +4252,136 @@
       <c r="A149" s="8">
         <v>148</v>
       </c>
+      <c r="B149" s="1">
+        <v>46262</v>
+      </c>
+      <c r="C149" t="s">
+        <v>329</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
+      <c r="B150" s="1">
+        <v>46262</v>
+      </c>
+      <c r="C150" t="s">
+        <v>330</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
       </c>
+      <c r="B151" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C151" t="s">
+        <v>331</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>151</v>
       </c>
+      <c r="B152" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C152" t="s">
+        <v>332</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
+      <c r="B153" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C153" t="s">
+        <v>333</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
       </c>
+      <c r="B154" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C154" t="s">
+        <v>334</v>
+      </c>
+      <c r="D154" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E154" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>154</v>
       </c>
+      <c r="B155" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C155" t="s">
+        <v>335</v>
+      </c>
+      <c r="D155" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E155" s="17" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C156" t="s">
+        <v>336</v>
+      </c>
+      <c r="D156" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E156" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B713A5A5-F814-466E-9352-F02769BE4988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3997DA-6AA8-4441-A90B-FD8CB923F559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="339">
   <si>
     <t>London</t>
   </si>
@@ -1046,6 +1046,12 @@
   </si>
   <si>
     <t>The Colmore</t>
+  </si>
+  <si>
+    <t>The Windmill</t>
+  </si>
+  <si>
+    <t>Stansted Airport</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1595,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1637,7 +1643,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1699,7 +1705,7 @@
       </c>
       <c r="G8" s="12">
         <f>COUNTIF(E:E, "W")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4387,6 +4393,18 @@
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C157" t="s">
+        <v>337</v>
+      </c>
+      <c r="D157" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="E157" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3997DA-6AA8-4441-A90B-FD8CB923F559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94292061-3273-4C1B-A0ED-BE26EBC8E008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94292061-3273-4C1B-A0ED-BE26EBC8E008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D1B284-D03A-4D47-AD84-DD8DB36C1E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="344">
   <si>
     <t>London</t>
   </si>
@@ -1052,6 +1052,21 @@
   </si>
   <si>
     <t>Stansted Airport</t>
+  </si>
+  <si>
+    <t>Taverna Manola</t>
+  </si>
+  <si>
+    <t>Pserimos</t>
+  </si>
+  <si>
+    <t>gr</t>
+  </si>
+  <si>
+    <t>Mastihari</t>
+  </si>
+  <si>
+    <t>Harama</t>
   </si>
 </sst>
 </file>
@@ -1619,7 +1634,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1643,7 +1658,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6735,10 +6750,34 @@
       <c r="A107" s="8">
         <v>106</v>
       </c>
+      <c r="B107" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C107" t="s">
+        <v>343</v>
+      </c>
+      <c r="D107" t="s">
+        <v>342</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>107</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C108" t="s">
+        <v>339</v>
+      </c>
+      <c r="D108" t="s">
+        <v>340</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D1B284-D03A-4D47-AD84-DD8DB36C1E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6E96CF-7C13-448D-8331-694FEBBD8D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="347">
   <si>
     <t>London</t>
   </si>
@@ -1067,6 +1067,15 @@
   </si>
   <si>
     <t>Harama</t>
+  </si>
+  <si>
+    <t>Kalymnos</t>
+  </si>
+  <si>
+    <t>Manifesto</t>
+  </si>
+  <si>
+    <t>Fatolitis</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1643,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1658,7 +1667,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6784,10 +6793,34 @@
       <c r="A109" s="8">
         <v>108</v>
       </c>
+      <c r="B109" s="1">
+        <v>46270</v>
+      </c>
+      <c r="C109" t="s">
+        <v>345</v>
+      </c>
+      <c r="D109" t="s">
+        <v>344</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>109</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46270</v>
+      </c>
+      <c r="C110" t="s">
+        <v>346</v>
+      </c>
+      <c r="D110" t="s">
+        <v>344</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6E96CF-7C13-448D-8331-694FEBBD8D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C74E4F4-1FF3-404A-B971-0ACD6D7559CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="349">
   <si>
     <t>London</t>
   </si>
@@ -1076,6 +1076,12 @@
   </si>
   <si>
     <t>Fatolitis</t>
+  </si>
+  <si>
+    <t>Dimitris o Karaflas</t>
+  </si>
+  <si>
+    <t>Leros</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1649,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1667,7 +1673,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6827,6 +6833,18 @@
       <c r="A111" s="8">
         <v>110</v>
       </c>
+      <c r="B111" s="1">
+        <v>46272</v>
+      </c>
+      <c r="C111" t="s">
+        <v>347</v>
+      </c>
+      <c r="D111" t="s">
+        <v>348</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
